--- a/paper/test_results.xlsx
+++ b/paper/test_results.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mixture-of-Experts_Research\paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54713A94-E51B-4D37-849C-933AD8BA1CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D058737F-6797-4850-BE41-202350495F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F82E78F-F225-4B75-B204-CA5D83064DD0}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="16629" windowHeight="17880" activeTab="1" xr2:uid="{7F82E78F-F225-4B75-B204-CA5D83064DD0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="15">
   <si>
     <t>epsilon</t>
   </si>
@@ -76,13 +77,19 @@
   <si>
     <t>std</t>
   </si>
+  <si>
+    <t>Clean Acc</t>
+  </si>
+  <si>
+    <t>Adv Acc</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -207,42 +214,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,1559 +585,1559 @@
   <dimension ref="A2:N47"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.23046875" style="1"/>
-    <col min="2" max="2" width="12.4609375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9.23046875" style="1" customWidth="1"/>
-    <col min="5" max="9" width="9.23046875" style="1"/>
-    <col min="10" max="10" width="12.61328125" style="1" customWidth="1"/>
-    <col min="11" max="12" width="9.23046875" style="1"/>
-    <col min="13" max="13" width="10.84375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.07421875" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.23046875" style="1"/>
+    <col min="2" max="2" width="12.4609375" customWidth="1"/>
+    <col min="3" max="4" width="9.23046875" customWidth="1"/>
+    <col min="10" max="10" width="12.61328125" customWidth="1"/>
+    <col min="13" max="13" width="10.84375" customWidth="1"/>
+    <col min="14" max="14" width="7.07421875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="16"/>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="B3" s="18"/>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="13">
         <v>7.8399999999999997E-3</v>
       </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
         <v>19</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="1">
         <f>$N$10-D4-F4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3">
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1">
         <f>$N$10-G4-I4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="10">
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
         <f>(D4+G4)/($N$10*2)</f>
         <v>0.97499999999999998</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="2">
         <v>8.64</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="7">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="4">
         <v>2</v>
       </c>
-      <c r="D5" s="5">
-        <v>20</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
         <f>$N$10-D5-F5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>19</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <f>$N$10-G5-I5</f>
         <v>0</v>
       </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
         <f>(D5+G5)/($N$10*2)</f>
         <v>0.97499999999999998</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="4">
         <v>8.74</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="7">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="4">
         <v>3</v>
       </c>
-      <c r="D6" s="5">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
         <f>$N$10-D6-F6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>20</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
         <f>$N$10-G6-I6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
         <f>(D6+G6)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="4">
         <v>9.7899999999999991</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="7">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="4">
         <v>4</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7">
         <v>18</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <f>$N$10-D7-F7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="G7" s="17">
-        <v>20</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
         <f>$N$10-G7-I7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="17">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
         <f>(D7+G7)/($N$10*2)</f>
         <v>0.95</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="4">
         <v>8.73</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="7">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="4">
         <v>5</v>
       </c>
-      <c r="D8" s="17">
-        <v>20</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
         <f>$N$10-D8-F8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="17">
-        <v>0</v>
-      </c>
-      <c r="G8" s="17">
-        <v>20</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+      <c r="H8">
         <f>$N$10-G8-I8</f>
         <v>0</v>
       </c>
-      <c r="I8" s="17">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18">
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <f>(D8+G8)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="4">
         <v>9.48</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="9">
         <f>AVERAGE(D4:D8)</f>
         <v>19.399999999999999</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="9">
         <f t="shared" ref="E9:K9" si="0">AVERAGE(E4:E8)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="9">
         <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="9">
         <f t="shared" si="0"/>
         <v>19.8</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="9">
         <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="11">
         <f t="shared" si="0"/>
         <v>0.98000000000000009</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="6">
         <f t="shared" si="0"/>
         <v>9.0760000000000023</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A10" s="12"/>
-      <c r="B10" s="11">
+      <c r="A10" s="14"/>
+      <c r="B10" s="13">
         <v>1.5689999999999999E-2</v>
       </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3">
-        <v>20</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1">
         <f>$N$10-D10-F10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>20</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1">
         <f>$N$10-G10-I10</f>
         <v>0</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="10">
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
         <f>(D10+G10)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="2">
         <v>8.57</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="7">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="4">
         <v>2</v>
       </c>
-      <c r="D11" s="17">
-        <v>20</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
         <f t="shared" ref="E11:E14" si="1">$N$10-D11-F11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="17">
-        <v>0</v>
-      </c>
-      <c r="G11" s="17">
-        <v>20</v>
-      </c>
-      <c r="H11" s="5">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11">
         <f t="shared" ref="H11:H14" si="2">$N$10-G11-I11</f>
         <v>0</v>
       </c>
-      <c r="I11" s="17">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18">
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
         <f>(D11+G11)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="4">
         <v>9.1199999999999992</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="7">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="4">
         <v>3</v>
       </c>
-      <c r="D12" s="17">
-        <v>20</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>20</v>
-      </c>
-      <c r="H12" s="5">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
+      </c>
+      <c r="H12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18">
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <f t="shared" ref="J12:J14" si="3">(D12+G12)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="4">
         <v>8.48</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="7">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="4">
         <v>4</v>
       </c>
-      <c r="D13" s="17">
-        <v>20</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F13" s="17">
-        <v>0</v>
-      </c>
-      <c r="G13" s="17">
-        <v>20</v>
-      </c>
-      <c r="H13" s="5">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="17">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18">
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="4">
         <v>9.0399999999999991</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="7">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="4">
         <v>5</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14">
         <v>19</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F14" s="17">
-        <v>1</v>
-      </c>
-      <c r="G14" s="17">
-        <v>20</v>
-      </c>
-      <c r="H14" s="5">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>20</v>
+      </c>
+      <c r="H14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="17">
-        <v>0</v>
-      </c>
-      <c r="J14" s="18">
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <f t="shared" si="3"/>
         <v>0.97499999999999998</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="4">
         <v>8.57</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="9">
         <f>AVERAGE(D10:D14)</f>
         <v>19.8</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="9">
         <f t="shared" ref="E15" si="4">AVERAGE(E10:E14)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="9">
         <f t="shared" ref="F15" si="5">AVERAGE(F10:F14)</f>
         <v>0.2</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="9">
         <f t="shared" ref="G15" si="6">AVERAGE(G10:G14)</f>
         <v>20</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="9">
         <f t="shared" ref="H15" si="7">AVERAGE(H10:H14)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="9">
         <f t="shared" ref="I15" si="8">AVERAGE(I10:I14)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="11">
         <f t="shared" ref="J15" si="9">AVERAGE(J10:J14)</f>
         <v>0.99499999999999988</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="6">
         <f t="shared" ref="K15" si="10">AVERAGE(K10:K14)</f>
         <v>8.7559999999999985</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A16" s="12"/>
-      <c r="B16" s="11">
+      <c r="A16" s="14"/>
+      <c r="B16" s="13">
         <v>3.1370000000000002E-2</v>
       </c>
-      <c r="C16" s="4">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3">
-        <v>20</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1">
         <f>$N$10-D16-F16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
-        <v>20</v>
-      </c>
-      <c r="H16" s="3">
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>20</v>
+      </c>
+      <c r="H16" s="1">
         <f>$N$10-G16-I16</f>
         <v>0</v>
       </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="10">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7">
         <f>(D16+G16)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="2">
         <v>8.4700000000000006</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="7">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="4">
         <v>2</v>
       </c>
-      <c r="D17" s="17">
-        <v>20</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
         <f t="shared" ref="E17:E20" si="11">$N$10-D17-F17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="17">
-        <v>0</v>
-      </c>
-      <c r="G17" s="17">
-        <v>20</v>
-      </c>
-      <c r="H17" s="5">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17">
         <f t="shared" ref="H17:H20" si="12">$N$10-G17-I17</f>
         <v>0</v>
       </c>
-      <c r="I17" s="17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="18">
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
         <f>(D17+G17)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="4">
         <v>10.119999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="7">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="4">
         <v>3</v>
       </c>
-      <c r="D18" s="17">
-        <v>20</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18">
+        <v>20</v>
+      </c>
+      <c r="E18">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F18" s="17">
-        <v>0</v>
-      </c>
-      <c r="G18" s="17">
-        <v>20</v>
-      </c>
-      <c r="H18" s="5">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>20</v>
+      </c>
+      <c r="H18">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I18" s="17">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18">
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <f t="shared" ref="J18:J20" si="13">(D18+G18)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="4">
         <v>8.4600000000000009</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="7">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="4">
         <v>4</v>
       </c>
-      <c r="D19" s="17">
-        <v>20</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19">
+        <v>20</v>
+      </c>
+      <c r="E19">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F19" s="17">
-        <v>0</v>
-      </c>
-      <c r="G19" s="17">
-        <v>20</v>
-      </c>
-      <c r="H19" s="5">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I19" s="17">
-        <v>0</v>
-      </c>
-      <c r="J19" s="18">
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="4">
         <v>11.54</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="7">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="4">
         <v>5</v>
       </c>
-      <c r="D20" s="17">
-        <v>20</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20">
+        <v>20</v>
+      </c>
+      <c r="E20">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F20" s="17">
-        <v>0</v>
-      </c>
-      <c r="G20" s="17">
-        <v>20</v>
-      </c>
-      <c r="H20" s="5">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>20</v>
+      </c>
+      <c r="H20">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I20" s="17">
-        <v>0</v>
-      </c>
-      <c r="J20" s="18">
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="4">
         <v>8.57</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="9">
         <f>AVERAGE(D16:D20)</f>
         <v>20</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="9">
         <f t="shared" ref="E21" si="14">AVERAGE(E16:E20)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="9">
         <f t="shared" ref="F21" si="15">AVERAGE(F16:F20)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="9">
         <f t="shared" ref="G21" si="16">AVERAGE(G16:G20)</f>
         <v>20</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="9">
         <f t="shared" ref="H21" si="17">AVERAGE(H16:H20)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="9">
         <f t="shared" ref="I21" si="18">AVERAGE(I16:I20)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="5">
         <f t="shared" ref="J21" si="19">AVERAGE(J16:J20)</f>
         <v>1</v>
       </c>
-      <c r="K21" s="20">
+      <c r="K21" s="10">
         <f t="shared" ref="K21" si="20">AVERAGE(K16:K20)</f>
         <v>9.4320000000000004</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="12">
         <f>_xlfn.STDEV.S(D4:D8)</f>
         <v>0.89442719099991586</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="12">
         <f>_xlfn.STDEV.S(E4:E8)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="12">
         <f>_xlfn.STDEV.S(F4:F8)</f>
         <v>0.89442719099991586</v>
       </c>
-      <c r="G22" s="22">
-        <f t="shared" ref="E22:K22" si="21">_xlfn.STDEV.S(G4:G8)</f>
+      <c r="G22" s="12">
+        <f t="shared" ref="G22:K22" si="21">_xlfn.STDEV.S(G4:G8)</f>
         <v>0.44721359549995793</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="12">
         <f t="shared" si="21"/>
         <v>0.44721359549995793</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22" s="12">
         <f>_xlfn.STDEV.S(J4:J8)</f>
         <v>2.0916500663351906E-2</v>
       </c>
-      <c r="K22" s="22">
+      <c r="K22" s="12">
         <f t="shared" si="21"/>
         <v>0.52338322479804367</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="12">
         <f>_xlfn.STDEV.S(D10:D14)</f>
         <v>0.44721359549995793</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="12">
         <f t="shared" ref="E23:K23" si="22">_xlfn.STDEV.S(E10:E14)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="12">
         <f t="shared" si="22"/>
         <v>0.44721359549995793</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23" s="12">
         <f t="shared" si="22"/>
         <v>1.1180339887498959E-2</v>
       </c>
-      <c r="K23" s="22">
+      <c r="K23" s="12">
         <f t="shared" si="22"/>
         <v>0.29938269823087577</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="C24" s="17" t="s">
+      <c r="C24" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="12">
         <f>_xlfn.STDEV.S(D16:D20)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="12">
         <f t="shared" ref="E24:K24" si="23">_xlfn.STDEV.S(E16:E20)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K24" s="22">
+      <c r="K24" s="12">
         <f t="shared" si="23"/>
         <v>1.3720677825821823</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="13">
         <v>7.8399999999999997E-3</v>
       </c>
-      <c r="C27" s="4">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3">
-        <v>20</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="1">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1">
         <f>$N$10-D27-F27</f>
         <v>0</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>20</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>20</v>
+      </c>
+      <c r="H27" s="1">
         <f>$N$10-G27-I27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="10">
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7">
         <f>(D27+G27)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K27" s="4">
+      <c r="K27" s="2">
         <v>8.49</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="7">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="4">
         <v>2</v>
       </c>
-      <c r="D28" s="17">
-        <v>20</v>
-      </c>
-      <c r="E28" s="5">
+      <c r="D28">
+        <v>20</v>
+      </c>
+      <c r="E28">
         <f>$N$10-D28-F28</f>
         <v>0</v>
       </c>
-      <c r="F28" s="17">
-        <v>0</v>
-      </c>
-      <c r="G28" s="17">
-        <v>20</v>
-      </c>
-      <c r="H28" s="5">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>20</v>
+      </c>
+      <c r="H28">
         <f>$N$10-G28-I28</f>
         <v>0</v>
       </c>
-      <c r="I28" s="17">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6">
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
         <f>(D28+G28)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="4">
         <v>10.29</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="7">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="4">
         <v>3</v>
       </c>
-      <c r="D29" s="17">
-        <v>20</v>
-      </c>
-      <c r="E29" s="5">
+      <c r="D29">
+        <v>20</v>
+      </c>
+      <c r="E29">
         <f t="shared" ref="E29:E31" si="24">$N$10-D29-F29</f>
         <v>0</v>
       </c>
-      <c r="F29" s="17">
-        <v>0</v>
-      </c>
-      <c r="G29" s="17">
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
         <v>18</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29">
         <f>$N$10-G29-I29</f>
         <v>0</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29">
         <v>2</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="3">
         <f>(D29+G29)/($N$10*2)</f>
         <v>0.95</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="4">
         <v>8.58</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="7">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="4">
         <v>4</v>
       </c>
-      <c r="D30" s="17">
-        <v>20</v>
-      </c>
-      <c r="E30" s="5">
+      <c r="D30">
+        <v>20</v>
+      </c>
+      <c r="E30">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F30" s="17">
-        <v>0</v>
-      </c>
-      <c r="G30" s="17">
-        <v>20</v>
-      </c>
-      <c r="H30" s="5">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>20</v>
+      </c>
+      <c r="H30">
         <f t="shared" ref="H30:H31" si="25">$N$10-G30-I30</f>
         <v>0</v>
       </c>
-      <c r="I30" s="17">
-        <v>0</v>
-      </c>
-      <c r="J30" s="6">
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
         <f>(D30+G30)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="4">
         <v>8.43</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="7">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="4">
         <v>5</v>
       </c>
-      <c r="D31" s="17">
-        <v>20</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="D31">
+        <v>20</v>
+      </c>
+      <c r="E31">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F31" s="17">
-        <v>0</v>
-      </c>
-      <c r="G31" s="17">
-        <v>20</v>
-      </c>
-      <c r="H31" s="5">
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>20</v>
+      </c>
+      <c r="H31">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I31" s="17">
-        <v>0</v>
-      </c>
-      <c r="J31" s="18">
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
         <f>(D31+G31)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="4">
         <v>10.01</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="14" t="s">
+      <c r="A32" s="14"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="9">
         <f>AVERAGE(D27:D31)</f>
         <v>20</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="9">
         <f t="shared" ref="E32" si="26">AVERAGE(E27:E31)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="9">
         <f t="shared" ref="F32" si="27">AVERAGE(F27:F31)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="9">
         <f t="shared" ref="G32" si="28">AVERAGE(G27:G31)</f>
         <v>19.600000000000001</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="9">
         <f t="shared" ref="H32" si="29">AVERAGE(H27:H31)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="9">
         <f t="shared" ref="I32" si="30">AVERAGE(I27:I31)</f>
         <v>0.4</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="5">
         <f t="shared" ref="J32" si="31">AVERAGE(J27:J31)</f>
         <v>0.99</v>
       </c>
-      <c r="K32" s="20">
+      <c r="K32" s="10">
         <f t="shared" ref="K32" si="32">AVERAGE(K27:K31)</f>
         <v>9.16</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A33" s="12"/>
-      <c r="B33" s="11">
+      <c r="A33" s="14"/>
+      <c r="B33" s="13">
         <v>1.5689999999999999E-2</v>
       </c>
-      <c r="C33" s="4">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3">
-        <v>20</v>
-      </c>
-      <c r="E33" s="5">
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>20</v>
+      </c>
+      <c r="E33">
         <f t="shared" ref="E33:E37" si="33">$N$10-D33-F33</f>
         <v>0</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
         <v>19</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33">
         <f t="shared" ref="H33:H37" si="34">$N$10-G33-I33</f>
         <v>0</v>
       </c>
-      <c r="I33" s="3">
-        <v>1</v>
-      </c>
-      <c r="J33" s="10">
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="7">
         <f>(D33+G33)/($N$10*2)</f>
         <v>0.97499999999999998</v>
       </c>
-      <c r="K33" s="4">
+      <c r="K33" s="2">
         <v>8.58</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="7">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="4">
         <v>2</v>
       </c>
-      <c r="D34" s="17">
-        <v>20</v>
-      </c>
-      <c r="E34" s="5">
+      <c r="D34">
+        <v>20</v>
+      </c>
+      <c r="E34">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="F34" s="17">
-        <v>0</v>
-      </c>
-      <c r="G34" s="17">
-        <v>20</v>
-      </c>
-      <c r="H34" s="5">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>20</v>
+      </c>
+      <c r="H34">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="I34" s="17">
-        <v>0</v>
-      </c>
-      <c r="J34" s="6">
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
         <f t="shared" ref="J34:J37" si="35">(D34+G34)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="4">
         <v>9.93</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="7">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="4">
         <v>3</v>
       </c>
-      <c r="D35" s="17">
-        <v>20</v>
-      </c>
-      <c r="E35" s="5">
+      <c r="D35">
+        <v>20</v>
+      </c>
+      <c r="E35">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="F35" s="17">
-        <v>0</v>
-      </c>
-      <c r="G35" s="17">
-        <v>20</v>
-      </c>
-      <c r="H35" s="5">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>20</v>
+      </c>
+      <c r="H35">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="I35" s="17">
-        <v>0</v>
-      </c>
-      <c r="J35" s="6">
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <f t="shared" si="35"/>
         <v>1</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="4">
         <v>8.4700000000000006</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="7">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="4">
         <v>4</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36">
         <v>19</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="F36" s="17">
-        <v>1</v>
-      </c>
-      <c r="G36" s="17">
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
         <v>19</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="I36" s="17">
-        <v>1</v>
-      </c>
-      <c r="J36" s="6">
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
         <f t="shared" si="35"/>
         <v>0.95</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K36" s="4">
         <v>8.6300000000000008</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="7">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="4">
         <v>5</v>
       </c>
-      <c r="D37" s="17">
-        <v>20</v>
-      </c>
-      <c r="E37" s="5">
+      <c r="D37">
+        <v>20</v>
+      </c>
+      <c r="E37">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="F37" s="17">
-        <v>0</v>
-      </c>
-      <c r="G37" s="17">
-        <v>20</v>
-      </c>
-      <c r="H37" s="5">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>20</v>
+      </c>
+      <c r="H37">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="I37" s="17">
-        <v>0</v>
-      </c>
-      <c r="J37" s="6">
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
         <f t="shared" si="35"/>
         <v>1</v>
       </c>
-      <c r="K37" s="7">
+      <c r="K37" s="4">
         <v>9.76</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="14" t="s">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="9">
         <f>AVERAGE(D33:D37)</f>
         <v>19.8</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="9">
         <f t="shared" ref="E38" si="36">AVERAGE(E33:E37)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="9">
         <f t="shared" ref="F38" si="37">AVERAGE(F33:F37)</f>
         <v>0.2</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="9">
         <f t="shared" ref="G38" si="38">AVERAGE(G33:G37)</f>
         <v>19.600000000000001</v>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="9">
         <f t="shared" ref="H38" si="39">AVERAGE(H33:H37)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="9">
         <f t="shared" ref="I38" si="40">AVERAGE(I33:I37)</f>
         <v>0.4</v>
       </c>
-      <c r="J38" s="8">
+      <c r="J38" s="5">
         <f t="shared" ref="J38" si="41">AVERAGE(J33:J37)</f>
         <v>0.98499999999999999</v>
       </c>
-      <c r="K38" s="20">
+      <c r="K38" s="10">
         <f t="shared" ref="K38" si="42">AVERAGE(K33:K37)</f>
         <v>9.0739999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A39" s="12"/>
-      <c r="B39" s="11">
+      <c r="A39" s="14"/>
+      <c r="B39" s="13">
         <v>3.1370000000000002E-2</v>
       </c>
-      <c r="C39" s="4">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3">
-        <v>20</v>
-      </c>
-      <c r="E39" s="3">
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1">
+        <v>20</v>
+      </c>
+      <c r="E39" s="1">
         <f>$N$10-D39-F39</f>
         <v>0</v>
       </c>
-      <c r="F39" s="3">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3">
-        <v>20</v>
-      </c>
-      <c r="H39" s="3">
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>20</v>
+      </c>
+      <c r="H39" s="1">
         <f>$N$10-G39-I39</f>
         <v>0</v>
       </c>
-      <c r="I39" s="3">
-        <v>0</v>
-      </c>
-      <c r="J39" s="10">
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="7">
         <f>(D39+G39)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K39" s="4">
+      <c r="K39" s="2">
         <v>8.57</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="7">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="4">
         <v>2</v>
       </c>
-      <c r="D40" s="17">
-        <v>20</v>
-      </c>
-      <c r="E40" s="5">
+      <c r="D40">
+        <v>20</v>
+      </c>
+      <c r="E40">
         <f t="shared" ref="E40:E43" si="43">$N$10-D40-F40</f>
         <v>0</v>
       </c>
-      <c r="F40" s="17">
-        <v>0</v>
-      </c>
-      <c r="G40" s="17">
-        <v>20</v>
-      </c>
-      <c r="H40" s="5">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>20</v>
+      </c>
+      <c r="H40">
         <f t="shared" ref="H40:H43" si="44">$N$10-G40-I40</f>
         <v>0</v>
       </c>
-      <c r="I40" s="17">
-        <v>0</v>
-      </c>
-      <c r="J40" s="6">
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
         <f t="shared" ref="J40:J43" si="45">(D40+G40)/($N$10*2)</f>
         <v>1</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K40" s="4">
         <v>10.49</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="7">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="4">
         <v>3</v>
       </c>
-      <c r="D41" s="17">
-        <v>20</v>
-      </c>
-      <c r="E41" s="5">
+      <c r="D41">
+        <v>20</v>
+      </c>
+      <c r="E41">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F41" s="17">
-        <v>0</v>
-      </c>
-      <c r="G41" s="17">
-        <v>20</v>
-      </c>
-      <c r="H41" s="5">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>20</v>
+      </c>
+      <c r="H41">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="I41" s="17">
-        <v>0</v>
-      </c>
-      <c r="J41" s="6">
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <f t="shared" si="45"/>
         <v>1</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K41" s="4">
         <v>8.66</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="7">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="4">
         <v>4</v>
       </c>
-      <c r="D42" s="17">
-        <v>20</v>
-      </c>
-      <c r="E42" s="5">
+      <c r="D42">
+        <v>20</v>
+      </c>
+      <c r="E42">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F42" s="17">
-        <v>0</v>
-      </c>
-      <c r="G42" s="17">
-        <v>20</v>
-      </c>
-      <c r="H42" s="5">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>20</v>
+      </c>
+      <c r="H42">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="I42" s="17">
-        <v>0</v>
-      </c>
-      <c r="J42" s="6">
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <f t="shared" si="45"/>
         <v>1</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K42" s="4">
         <v>8.58</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="7">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="4">
         <v>5</v>
       </c>
-      <c r="D43" s="17">
-        <v>20</v>
-      </c>
-      <c r="E43" s="5">
+      <c r="D43">
+        <v>20</v>
+      </c>
+      <c r="E43">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F43" s="17">
-        <v>0</v>
-      </c>
-      <c r="G43" s="17">
-        <v>20</v>
-      </c>
-      <c r="H43" s="5">
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>20</v>
+      </c>
+      <c r="H43">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="I43" s="17">
-        <v>0</v>
-      </c>
-      <c r="J43" s="6">
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <f t="shared" si="45"/>
         <v>1</v>
       </c>
-      <c r="K43" s="7">
+      <c r="K43" s="4">
         <v>9.94</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14" t="s">
+      <c r="A44" s="15"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="9">
         <f>AVERAGE(D39:D43)</f>
         <v>20</v>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="9">
         <f t="shared" ref="E44" si="46">AVERAGE(E39:E43)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="9">
         <f t="shared" ref="F44" si="47">AVERAGE(F39:F43)</f>
         <v>0</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="9">
         <f t="shared" ref="G44" si="48">AVERAGE(G39:G43)</f>
         <v>20</v>
       </c>
-      <c r="H44" s="19">
+      <c r="H44" s="9">
         <f t="shared" ref="H44" si="49">AVERAGE(H39:H43)</f>
         <v>0</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="9">
         <f t="shared" ref="I44" si="50">AVERAGE(I39:I43)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="8">
+      <c r="J44" s="5">
         <f t="shared" ref="J44" si="51">AVERAGE(J39:J43)</f>
         <v>1</v>
       </c>
-      <c r="K44" s="20">
+      <c r="K44" s="10">
         <f t="shared" ref="K44" si="52">AVERAGE(K39:K43)</f>
         <v>9.2480000000000011</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>12</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="12">
         <f>_xlfn.STDEV.S(D27:D31)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="12">
         <f>_xlfn.STDEV.S(E27:E31)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="12">
         <f>_xlfn.STDEV.S(F27:F31)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="22">
-        <f t="shared" ref="G45:K45" si="53">_xlfn.STDEV.S(G27:G31)</f>
+      <c r="G45" s="12">
+        <f t="shared" ref="G45:I45" si="53">_xlfn.STDEV.S(G27:G31)</f>
         <v>0.89442719099991586</v>
       </c>
-      <c r="H45" s="22">
+      <c r="H45" s="12">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45" s="12">
         <f t="shared" si="53"/>
         <v>0.89442719099991586</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45" s="12">
         <f>_xlfn.STDEV.S(J27:J31)</f>
         <v>2.2360679774997918E-2</v>
       </c>
-      <c r="K45" s="22">
+      <c r="K45" s="12">
         <f t="shared" ref="K45" si="54">_xlfn.STDEV.S(K27:K31)</f>
         <v>0.91071400560219751</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>12</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="12">
         <f>_xlfn.STDEV.S(D33:D37)</f>
         <v>0.44721359549995793</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="12">
         <f t="shared" ref="E46:K46" si="55">_xlfn.STDEV.S(E33:E37)</f>
         <v>0</v>
       </c>
-      <c r="F46" s="22">
+      <c r="F46" s="12">
         <f t="shared" si="55"/>
         <v>0.44721359549995793</v>
       </c>
-      <c r="G46" s="22">
+      <c r="G46" s="12">
         <f t="shared" si="55"/>
         <v>0.54772255750516607</v>
       </c>
-      <c r="H46" s="22">
+      <c r="H46" s="12">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="I46" s="22">
+      <c r="I46" s="12">
         <f t="shared" si="55"/>
         <v>0.54772255750516607</v>
       </c>
-      <c r="J46" s="22">
+      <c r="J46" s="12">
         <f t="shared" si="55"/>
         <v>2.2360679774997918E-2</v>
       </c>
-      <c r="K46" s="22">
+      <c r="K46" s="12">
         <f t="shared" si="55"/>
         <v>0.70875242503994251</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="C47" s="17" t="s">
+      <c r="C47" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="12">
         <f>_xlfn.STDEV.S(D39:D43)</f>
         <v>0</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="12">
         <f t="shared" ref="E47:K47" si="56">_xlfn.STDEV.S(E39:E43)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="12">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="12">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="12">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47" s="12">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47" s="12">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="K47" s="22">
+      <c r="K47" s="12">
         <f t="shared" si="56"/>
         <v>0.90458277675401266</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="B10:B15"/>
     <mergeCell ref="B16:B21"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A4:A21"/>
@@ -2141,12 +2145,391 @@
     <mergeCell ref="B27:B32"/>
     <mergeCell ref="B33:B38"/>
     <mergeCell ref="B39:B44"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="B10:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7419F7-AE6D-458E-87E6-B4E28D246AFC}">
+  <dimension ref="A2:H21"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="13.84375" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" customWidth="1"/>
+    <col min="6" max="6" width="14.61328125" customWidth="1"/>
+    <col min="7" max="7" width="9.23046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="17"/>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.47189999999999999</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.84099999999999997</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="17"/>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.99239999999999995</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.62019999999999997</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.83779999999999999</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="17"/>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.99209999999999998</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.52569999999999995</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="17"/>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.99139999999999995</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.53390000000000004</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.83750000000000002</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="17"/>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.60709999999999997</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="17"/>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="19">
+        <f>AVERAGE(C4:C8)</f>
+        <v>0.99177999999999999</v>
+      </c>
+      <c r="D9" s="19">
+        <f t="shared" ref="D9:F9" si="0">AVERAGE(D4:D8)</f>
+        <v>0.55176000000000003</v>
+      </c>
+      <c r="E9" s="19">
+        <f t="shared" si="0"/>
+        <v>0.83805999999999992</v>
+      </c>
+      <c r="F9" s="19">
+        <f t="shared" si="0"/>
+        <v>1.2000000000000002E-4</v>
+      </c>
+      <c r="H9" s="3">
+        <f>C9-D9</f>
+        <v>0.44001999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="17"/>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="19">
+        <f>_xlfn.STDEV.S(C4:C8)</f>
+        <v>5.6745043836443855E-4</v>
+      </c>
+      <c r="D10" s="19">
+        <f t="shared" ref="D10:F10" si="1">_xlfn.STDEV.S(D4:D8)</f>
+        <v>6.1486323682588141E-2</v>
+      </c>
+      <c r="E10" s="19">
+        <f t="shared" si="1"/>
+        <v>1.8215378118501926E-3</v>
+      </c>
+      <c r="F10" s="19">
+        <f t="shared" si="1"/>
+        <v>1.0954451150103323E-4</v>
+      </c>
+      <c r="H10" s="3">
+        <f>E9-F9</f>
+        <v>0.83793999999999991</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C11" t="str">
+        <f>TEXT(C9,"0.00%") &amp; " ± " &amp; TEXT(C10,"0.00%")</f>
+        <v>99.18% ± 0.06%</v>
+      </c>
+      <c r="D11" t="str">
+        <f>TEXT(D9,"0.00%") &amp; " ± " &amp; TEXT(D10,"0.00%")</f>
+        <v>55.18% ± 6.15%</v>
+      </c>
+      <c r="E11" t="str">
+        <f>TEXT(E9,"0.00%") &amp; " ± " &amp; TEXT(E10,"0.00%")</f>
+        <v>83.81% ± 0.18%</v>
+      </c>
+      <c r="F11" t="str">
+        <f>TEXT(F9,"0.00%") &amp; " ± " &amp; TEXT(F10,"0.00%")</f>
+        <v>0.01% ± 0.01%</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="17"/>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.99150000000000005</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.87870000000000004</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.77580000000000005</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.1704</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="17"/>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.99070000000000003</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.94769999999999999</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.77559999999999996</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="17"/>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.99060000000000004</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.94399999999999995</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.77669999999999995</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.17879999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="17"/>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.99139999999999995</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.96519999999999995</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.77839999999999998</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="17"/>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.99209999999999998</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.87960000000000005</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.77659999999999996</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.16950000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" s="17"/>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="19">
+        <f>AVERAGE(C14:C18)</f>
+        <v>0.99126000000000014</v>
+      </c>
+      <c r="D19" s="19">
+        <f t="shared" ref="D19" si="2">AVERAGE(D14:D18)</f>
+        <v>0.92303999999999997</v>
+      </c>
+      <c r="E19" s="19">
+        <f t="shared" ref="E19" si="3">AVERAGE(E14:E18)</f>
+        <v>0.77661999999999998</v>
+      </c>
+      <c r="F19" s="19">
+        <f t="shared" ref="F19" si="4">AVERAGE(F14:F18)</f>
+        <v>0.17133999999999999</v>
+      </c>
+      <c r="H19" s="3">
+        <f>C19-D19</f>
+        <v>6.8220000000000169E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="17"/>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="19">
+        <f>_xlfn.STDEV.S(C14:C18)</f>
+        <v>6.1886993787061242E-4</v>
+      </c>
+      <c r="D20" s="19">
+        <f t="shared" ref="D20:F20" si="5">_xlfn.STDEV.S(D14:D18)</f>
+        <v>4.0859429756177415E-2</v>
+      </c>
+      <c r="E20" s="19">
+        <f t="shared" si="5"/>
+        <v>1.1054410884348315E-3</v>
+      </c>
+      <c r="F20" s="19">
+        <f t="shared" si="5"/>
+        <v>4.4404954678503973E-3</v>
+      </c>
+      <c r="H20" s="3">
+        <f>E19-F19</f>
+        <v>0.60528000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C21" t="str">
+        <f>TEXT(C19,"0.00%") &amp; " ± " &amp; TEXT(C20,"0.00%")</f>
+        <v>99.13% ± 0.06%</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" ref="D21:F21" si="6">TEXT(D19,"0.00%") &amp; " ± " &amp; TEXT(D20,"0.00%")</f>
+        <v>92.30% ± 4.09%</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="6"/>
+        <v>77.66% ± 0.11%</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="6"/>
+        <v>17.13% ± 0.44%</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A10"/>
+    <mergeCell ref="A13:A20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/paper/test_results.xlsx
+++ b/paper/test_results.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mixture-of-Experts_Research\paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D058737F-6797-4850-BE41-202350495F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F81F083-49FD-4FA8-9465-44F36FC8F5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="16629" windowHeight="17880" activeTab="1" xr2:uid="{7F82E78F-F225-4B75-B204-CA5D83064DD0}"/>
+    <workbookView xWindow="74355" yWindow="0" windowWidth="12150" windowHeight="15585" xr2:uid="{7F82E78F-F225-4B75-B204-CA5D83064DD0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Empirical_Results_Experts" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -228,6 +228,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -238,15 +242,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,6 +581,398 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7419F7-AE6D-458E-87E6-B4E28D246AFC}">
+  <dimension ref="A2:H25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="13.84375" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" customWidth="1"/>
+    <col min="6" max="6" width="14.61328125" customWidth="1"/>
+    <col min="7" max="7" width="9.23046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="18"/>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.99209999999999998</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.58819999999999995</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="18"/>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.99270000000000003</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.43640000000000001</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.83879999999999999</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="18"/>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.4244</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.83550000000000002</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="18"/>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.99150000000000005</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.83789999999999998</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="18"/>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.46250000000000002</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.83530000000000004</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="18"/>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="13">
+        <f>AVERAGE(C4:C8)</f>
+        <v>0.99185999999999996</v>
+      </c>
+      <c r="D9" s="13">
+        <f t="shared" ref="D9:F9" si="0">AVERAGE(D4:D8)</f>
+        <v>0.46057999999999993</v>
+      </c>
+      <c r="E9" s="13">
+        <f t="shared" si="0"/>
+        <v>0.83750000000000002</v>
+      </c>
+      <c r="F9" s="13">
+        <f t="shared" si="0"/>
+        <v>1E-4</v>
+      </c>
+      <c r="H9" s="3">
+        <f>C9-D9</f>
+        <v>0.53127999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="18"/>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="13">
+        <f>_xlfn.STDEV.S(C4:C8)</f>
+        <v>6.4265076052238772E-4</v>
+      </c>
+      <c r="D10" s="13">
+        <f t="shared" ref="D10:F10" si="1">_xlfn.STDEV.S(D4:D8)</f>
+        <v>7.5779429926597017E-2</v>
+      </c>
+      <c r="E10" s="13">
+        <f t="shared" si="1"/>
+        <v>2.0579115627256395E-3</v>
+      </c>
+      <c r="F10" s="13">
+        <f t="shared" si="1"/>
+        <v>7.0710678118654754E-5</v>
+      </c>
+      <c r="H10" s="3">
+        <f>E9-F9</f>
+        <v>0.83740000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C11" t="str">
+        <f>TEXT(C9,"0.00%") &amp; " ± " &amp; TEXT(C10,"0.00%")</f>
+        <v>99.19% ± 0.06%</v>
+      </c>
+      <c r="D11" t="str">
+        <f>TEXT(D9,"0.00%") &amp; " ± " &amp; TEXT(D10,"0.00%")</f>
+        <v>46.06% ± 7.58%</v>
+      </c>
+      <c r="E11" t="str">
+        <f>TEXT(E9,"0.00%") &amp; " ± " &amp; TEXT(E10,"0.00%")</f>
+        <v>83.75% ± 0.21%</v>
+      </c>
+      <c r="F11" t="str">
+        <f>TEXT(F9,"0.00%") &amp; " ± " &amp; TEXT(F10,"0.00%")</f>
+        <v>0.01% ± 0.01%</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="18"/>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.99170000000000003</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.92849999999999999</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.17269999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="18"/>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.99119999999999997</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.81410000000000005</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.77229999999999999</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.1719</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="18"/>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.9919</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.92369999999999997</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.77310000000000001</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.17199999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="18"/>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.99150000000000005</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.9556</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.77590000000000003</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.17660000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="18"/>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.91669999999999996</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.77769999999999995</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.16900000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" s="18"/>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="13">
+        <f>AVERAGE(C14:C18)</f>
+        <v>0.9916600000000001</v>
+      </c>
+      <c r="D19" s="13">
+        <f t="shared" ref="D19" si="2">AVERAGE(D14:D18)</f>
+        <v>0.90771999999999997</v>
+      </c>
+      <c r="E19" s="13">
+        <f t="shared" ref="E19" si="3">AVERAGE(E14:E18)</f>
+        <v>0.77539999999999998</v>
+      </c>
+      <c r="F19" s="13">
+        <f t="shared" ref="F19" si="4">AVERAGE(F14:F18)</f>
+        <v>0.17243999999999998</v>
+      </c>
+      <c r="H19" s="3">
+        <f>C19-D19</f>
+        <v>8.3940000000000126E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="18"/>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="13">
+        <f>_xlfn.STDEV.S(C14:C18)</f>
+        <v>3.2093613071762869E-4</v>
+      </c>
+      <c r="D20" s="13">
+        <f t="shared" ref="D20:F20" si="5">_xlfn.STDEV.S(D14:D18)</f>
+        <v>5.4371426319345321E-2</v>
+      </c>
+      <c r="E20" s="13">
+        <f t="shared" si="5"/>
+        <v>2.6076809620810574E-3</v>
+      </c>
+      <c r="F20" s="13">
+        <f t="shared" si="5"/>
+        <v>2.7245183060497129E-3</v>
+      </c>
+      <c r="H20" s="3">
+        <f>E19-F19</f>
+        <v>0.60295999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C21" t="str">
+        <f>TEXT(C19,"0.00%") &amp; " ± " &amp; TEXT(C20,"0.00%")</f>
+        <v>99.17% ± 0.03%</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" ref="D21:F21" si="6">TEXT(D19,"0.00%") &amp; " ± " &amp; TEXT(D20,"0.00%")</f>
+        <v>90.77% ± 5.44%</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="6"/>
+        <v>77.54% ± 0.26%</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="6"/>
+        <v>17.24% ± 0.27%</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A3:A10"/>
+    <mergeCell ref="A13:A20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298A52AC-B951-4303-84A2-1510182D5632}">
   <dimension ref="A2:N47"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -593,22 +985,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B2" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="16" t="s">
+      <c r="B2" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="18"/>
+      <c r="B3" s="19"/>
       <c r="D3" t="s">
         <v>1</v>
       </c>
@@ -635,10 +1027,10 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="15">
         <v>7.8399999999999997E-3</v>
       </c>
       <c r="C4" s="2">
@@ -673,8 +1065,8 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="4">
         <v>2</v>
       </c>
@@ -707,8 +1099,8 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="4">
         <v>3</v>
       </c>
@@ -741,8 +1133,8 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="4">
         <v>4</v>
       </c>
@@ -775,8 +1167,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="4">
         <v>5</v>
       </c>
@@ -809,8 +1201,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="8" t="s">
         <v>8</v>
       </c>
@@ -848,8 +1240,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A10" s="14"/>
-      <c r="B10" s="13">
+      <c r="A10" s="16"/>
+      <c r="B10" s="15">
         <v>1.5689999999999999E-2</v>
       </c>
       <c r="C10" s="2">
@@ -890,8 +1282,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="4">
         <v>2</v>
       </c>
@@ -924,8 +1316,8 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="4">
         <v>3</v>
       </c>
@@ -958,8 +1350,8 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="4">
         <v>4</v>
       </c>
@@ -992,8 +1384,8 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="4">
         <v>5</v>
       </c>
@@ -1026,8 +1418,8 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="8" t="s">
         <v>8</v>
       </c>
@@ -1065,8 +1457,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A16" s="14"/>
-      <c r="B16" s="13">
+      <c r="A16" s="16"/>
+      <c r="B16" s="15">
         <v>3.1370000000000002E-2</v>
       </c>
       <c r="C16" s="2">
@@ -1101,8 +1493,8 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="4">
         <v>2</v>
       </c>
@@ -1135,8 +1527,8 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="4">
         <v>3</v>
       </c>
@@ -1169,8 +1561,8 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="4">
         <v>4</v>
       </c>
@@ -1203,8 +1595,8 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="4">
         <v>5</v>
       </c>
@@ -1237,8 +1629,8 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="8" t="s">
         <v>8</v>
       </c>
@@ -1387,10 +1779,10 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="15">
         <v>7.8399999999999997E-3</v>
       </c>
       <c r="C27" s="2">
@@ -1425,8 +1817,8 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="4">
         <v>2</v>
       </c>
@@ -1459,8 +1851,8 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="4">
         <v>3</v>
       </c>
@@ -1493,8 +1885,8 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="4">
         <v>4</v>
       </c>
@@ -1527,8 +1919,8 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="4">
         <v>5</v>
       </c>
@@ -1561,8 +1953,8 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A32" s="14"/>
-      <c r="B32" s="15"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="8" t="s">
         <v>8</v>
       </c>
@@ -1600,8 +1992,8 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A33" s="14"/>
-      <c r="B33" s="13">
+      <c r="A33" s="16"/>
+      <c r="B33" s="15">
         <v>1.5689999999999999E-2</v>
       </c>
       <c r="C33" s="2">
@@ -1636,8 +2028,8 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
       <c r="C34" s="4">
         <v>2</v>
       </c>
@@ -1670,8 +2062,8 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
       <c r="C35" s="4">
         <v>3</v>
       </c>
@@ -1704,8 +2096,8 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
       <c r="C36" s="4">
         <v>4</v>
       </c>
@@ -1738,8 +2130,8 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
       <c r="C37" s="4">
         <v>5</v>
       </c>
@@ -1772,8 +2164,8 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A38" s="14"/>
-      <c r="B38" s="15"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="17"/>
       <c r="C38" s="8" t="s">
         <v>8</v>
       </c>
@@ -1811,8 +2203,8 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A39" s="14"/>
-      <c r="B39" s="13">
+      <c r="A39" s="16"/>
+      <c r="B39" s="15">
         <v>3.1370000000000002E-2</v>
       </c>
       <c r="C39" s="2">
@@ -1847,8 +2239,8 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="4">
         <v>2</v>
       </c>
@@ -1881,8 +2273,8 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
+      <c r="A41" s="16"/>
+      <c r="B41" s="16"/>
       <c r="C41" s="4">
         <v>3</v>
       </c>
@@ -1915,8 +2307,8 @@
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
       <c r="C42" s="4">
         <v>4</v>
       </c>
@@ -1949,8 +2341,8 @@
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
       <c r="C43" s="4">
         <v>5</v>
       </c>
@@ -1983,8 +2375,8 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
       <c r="C44" s="8" t="s">
         <v>8</v>
       </c>
@@ -2134,402 +2526,19 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A4:A21"/>
+    <mergeCell ref="A27:A44"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B33:B38"/>
+    <mergeCell ref="B39:B44"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="B16:B21"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A21"/>
-    <mergeCell ref="A27:A44"/>
-    <mergeCell ref="B27:B32"/>
-    <mergeCell ref="B33:B38"/>
-    <mergeCell ref="B39:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7419F7-AE6D-458E-87E6-B4E28D246AFC}">
-  <dimension ref="A2:H21"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="3" max="3" width="13.84375" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="13.3046875" customWidth="1"/>
-    <col min="6" max="6" width="14.61328125" customWidth="1"/>
-    <col min="7" max="7" width="9.23046875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" s="17"/>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.99099999999999999</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.47189999999999999</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.84099999999999997</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" s="17"/>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.99239999999999995</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.62019999999999997</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.83779999999999999</v>
-      </c>
-      <c r="F5" s="3">
-        <v>2.9999999999999997E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="17"/>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.99209999999999998</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0.52569999999999995</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.83599999999999997</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="17"/>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.99139999999999995</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.53390000000000004</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.83750000000000002</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="17"/>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.60709999999999997</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.83799999999999997</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="17"/>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="19">
-        <f>AVERAGE(C4:C8)</f>
-        <v>0.99177999999999999</v>
-      </c>
-      <c r="D9" s="19">
-        <f t="shared" ref="D9:F9" si="0">AVERAGE(D4:D8)</f>
-        <v>0.55176000000000003</v>
-      </c>
-      <c r="E9" s="19">
-        <f t="shared" si="0"/>
-        <v>0.83805999999999992</v>
-      </c>
-      <c r="F9" s="19">
-        <f t="shared" si="0"/>
-        <v>1.2000000000000002E-4</v>
-      </c>
-      <c r="H9" s="3">
-        <f>C9-D9</f>
-        <v>0.44001999999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="17"/>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="19">
-        <f>_xlfn.STDEV.S(C4:C8)</f>
-        <v>5.6745043836443855E-4</v>
-      </c>
-      <c r="D10" s="19">
-        <f t="shared" ref="D10:F10" si="1">_xlfn.STDEV.S(D4:D8)</f>
-        <v>6.1486323682588141E-2</v>
-      </c>
-      <c r="E10" s="19">
-        <f t="shared" si="1"/>
-        <v>1.8215378118501926E-3</v>
-      </c>
-      <c r="F10" s="19">
-        <f t="shared" si="1"/>
-        <v>1.0954451150103323E-4</v>
-      </c>
-      <c r="H10" s="3">
-        <f>E9-F9</f>
-        <v>0.83793999999999991</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="C11" t="str">
-        <f>TEXT(C9,"0.00%") &amp; " ± " &amp; TEXT(C10,"0.00%")</f>
-        <v>99.18% ± 0.06%</v>
-      </c>
-      <c r="D11" t="str">
-        <f>TEXT(D9,"0.00%") &amp; " ± " &amp; TEXT(D10,"0.00%")</f>
-        <v>55.18% ± 6.15%</v>
-      </c>
-      <c r="E11" t="str">
-        <f>TEXT(E9,"0.00%") &amp; " ± " &amp; TEXT(E10,"0.00%")</f>
-        <v>83.81% ± 0.18%</v>
-      </c>
-      <c r="F11" t="str">
-        <f>TEXT(F9,"0.00%") &amp; " ± " &amp; TEXT(F10,"0.00%")</f>
-        <v>0.01% ± 0.01%</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="17"/>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3">
-        <v>0.99150000000000005</v>
-      </c>
-      <c r="D14" s="3">
-        <v>0.87870000000000004</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0.77580000000000005</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.1704</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="17"/>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" s="3">
-        <v>0.99070000000000003</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0.94769999999999999</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.77559999999999996</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.17100000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="17"/>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16" s="3">
-        <v>0.99060000000000004</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0.94399999999999995</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0.77669999999999995</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.17879999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" s="17"/>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17" s="3">
-        <v>0.99139999999999995</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0.96519999999999995</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0.77839999999999998</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.16700000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="17"/>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18" s="3">
-        <v>0.99209999999999998</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0.87960000000000005</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0.77659999999999996</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.16950000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" s="17"/>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="19">
-        <f>AVERAGE(C14:C18)</f>
-        <v>0.99126000000000014</v>
-      </c>
-      <c r="D19" s="19">
-        <f t="shared" ref="D19" si="2">AVERAGE(D14:D18)</f>
-        <v>0.92303999999999997</v>
-      </c>
-      <c r="E19" s="19">
-        <f t="shared" ref="E19" si="3">AVERAGE(E14:E18)</f>
-        <v>0.77661999999999998</v>
-      </c>
-      <c r="F19" s="19">
-        <f t="shared" ref="F19" si="4">AVERAGE(F14:F18)</f>
-        <v>0.17133999999999999</v>
-      </c>
-      <c r="H19" s="3">
-        <f>C19-D19</f>
-        <v>6.8220000000000169E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="17"/>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="19">
-        <f>_xlfn.STDEV.S(C14:C18)</f>
-        <v>6.1886993787061242E-4</v>
-      </c>
-      <c r="D20" s="19">
-        <f t="shared" ref="D20:F20" si="5">_xlfn.STDEV.S(D14:D18)</f>
-        <v>4.0859429756177415E-2</v>
-      </c>
-      <c r="E20" s="19">
-        <f t="shared" si="5"/>
-        <v>1.1054410884348315E-3</v>
-      </c>
-      <c r="F20" s="19">
-        <f t="shared" si="5"/>
-        <v>4.4404954678503973E-3</v>
-      </c>
-      <c r="H20" s="3">
-        <f>E19-F19</f>
-        <v>0.60528000000000004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="C21" t="str">
-        <f>TEXT(C19,"0.00%") &amp; " ± " &amp; TEXT(C20,"0.00%")</f>
-        <v>99.13% ± 0.06%</v>
-      </c>
-      <c r="D21" t="str">
-        <f t="shared" ref="D21:F21" si="6">TEXT(D19,"0.00%") &amp; " ± " &amp; TEXT(D20,"0.00%")</f>
-        <v>92.30% ± 4.09%</v>
-      </c>
-      <c r="E21" t="str">
-        <f t="shared" si="6"/>
-        <v>77.66% ± 0.11%</v>
-      </c>
-      <c r="F21" t="str">
-        <f t="shared" si="6"/>
-        <v>17.13% ± 0.44%</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A10"/>
-    <mergeCell ref="A13:A20"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/paper/test_results.xlsx
+++ b/paper/test_results.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mixture-of-Experts_Research\paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F81F083-49FD-4FA8-9465-44F36FC8F5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7292C7A-4A9F-46AD-9BB0-85A048747102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="74355" yWindow="0" windowWidth="12150" windowHeight="15585" xr2:uid="{7F82E78F-F225-4B75-B204-CA5D83064DD0}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{7F82E78F-F225-4B75-B204-CA5D83064DD0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Empirical_Results_Experts" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Empirical Results Experts" sheetId="2" r:id="rId1"/>
+    <sheet name="Formal Results Router" sheetId="1" r:id="rId2"/>
+    <sheet name="Formal Results Router old" sheetId="3" r:id="rId3"/>
+    <sheet name="Formal Results Expert" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="23">
   <si>
     <t>epsilon</t>
   </si>
@@ -83,13 +85,38 @@
   <si>
     <t>Adv Acc</t>
   </si>
+  <si>
+    <t>Fr</t>
+  </si>
+  <si>
+    <t>Average time (seconds per sample)</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>total num</t>
+  </si>
+  <si>
+    <t>MNIST NRT</t>
+  </si>
+  <si>
+    <t>CIFAR10 NRT</t>
+  </si>
+  <si>
+    <t>MNIST RT</t>
+  </si>
+  <si>
+    <t>CIFAR10 RT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -107,12 +134,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -214,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -232,6 +265,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -241,12 +284,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,17 +635,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="19"/>
+      <c r="E2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="14"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
@@ -620,7 +662,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" s="18"/>
+      <c r="A4" s="20"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -638,7 +680,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" s="18"/>
+      <c r="A5" s="20"/>
       <c r="B5">
         <v>2</v>
       </c>
@@ -656,7 +698,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="18"/>
+      <c r="A6" s="20"/>
       <c r="B6">
         <v>3</v>
       </c>
@@ -674,7 +716,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="18"/>
+      <c r="A7" s="20"/>
       <c r="B7">
         <v>4</v>
       </c>
@@ -692,7 +734,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="18"/>
+      <c r="A8" s="20"/>
       <c r="B8">
         <v>5</v>
       </c>
@@ -710,7 +752,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="18"/>
+      <c r="A9" s="20"/>
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -736,7 +778,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="18"/>
+      <c r="A10" s="20"/>
       <c r="B10" t="s">
         <v>12</v>
       </c>
@@ -780,7 +822,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C13" t="s">
@@ -797,7 +839,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="18"/>
+      <c r="A14" s="20"/>
       <c r="B14">
         <v>1</v>
       </c>
@@ -815,7 +857,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="18"/>
+      <c r="A15" s="20"/>
       <c r="B15">
         <v>2</v>
       </c>
@@ -833,7 +875,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="18"/>
+      <c r="A16" s="20"/>
       <c r="B16">
         <v>3</v>
       </c>
@@ -851,7 +893,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" s="18"/>
+      <c r="A17" s="20"/>
       <c r="B17">
         <v>4</v>
       </c>
@@ -869,7 +911,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="18"/>
+      <c r="A18" s="20"/>
       <c r="B18">
         <v>5</v>
       </c>
@@ -887,7 +929,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" s="18"/>
+      <c r="A19" s="20"/>
       <c r="B19" t="s">
         <v>8</v>
       </c>
@@ -913,7 +955,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="18"/>
+      <c r="A20" s="20"/>
       <c r="B20" t="s">
         <v>12</v>
       </c>
@@ -985,22 +1027,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="14" t="s">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14" t="s">
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="19"/>
+      <c r="B3" s="24"/>
       <c r="D3" t="s">
         <v>1</v>
       </c>
@@ -1023,257 +1065,181 @@
         <v>5</v>
       </c>
       <c r="K3" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="21">
         <v>7.8399999999999997E-3</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
-        <v>19</v>
-      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1">
         <f>$N$10-D4-F4</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>20</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="1">
         <f>$N$10-G4-I4</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="7">
         <f>(D4+G4)/($N$10*2)</f>
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="K4" s="2">
-        <v>8.64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="4">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
       <c r="E5">
         <f>$N$10-D5-F5</f>
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5">
         <f>$N$10-G5-I5</f>
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J5" s="3">
         <f>(D5+G5)/($N$10*2)</f>
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="K5" s="4">
-        <v>8.74</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="4">
         <v>3</v>
       </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
       <c r="E6">
         <f>$N$10-D6-F6</f>
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
         <v>20</v>
       </c>
       <c r="H6">
         <f>$N$10-G6-I6</f>
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J6" s="3">
         <f>(D6+G6)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K6" s="4">
-        <v>9.7899999999999991</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="4">
         <v>4</v>
       </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
       <c r="E7">
         <f>$N$10-D7-F7</f>
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
         <v>20</v>
       </c>
       <c r="H7">
         <f>$N$10-G7-I7</f>
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J7" s="3">
         <f>(D7+G7)/($N$10*2)</f>
-        <v>0.95</v>
-      </c>
-      <c r="K7" s="4">
-        <v>8.73</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="4">
         <v>5</v>
       </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
       <c r="E8">
         <f>$N$10-D8-F8</f>
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
         <v>20</v>
       </c>
       <c r="H8">
         <f>$N$10-G8-I8</f>
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J8" s="3">
         <f>(D8+G8)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K8" s="4">
-        <v>9.48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="4"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
       <c r="C9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="9" t="e">
         <f>AVERAGE(D4:D8)</f>
-        <v>19.399999999999999</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E9" s="9">
         <f t="shared" ref="E9:K9" si="0">AVERAGE(E4:E8)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="9">
+        <v>20</v>
+      </c>
+      <c r="F9" s="9" t="e">
         <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="G9" s="9">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G9" s="9" t="e">
         <f t="shared" si="0"/>
-        <v>19.8</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H9" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="9">
+        <v>20</v>
+      </c>
+      <c r="I9" s="9" t="e">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J9" s="11">
         <f t="shared" si="0"/>
-        <v>0.98000000000000009</v>
-      </c>
-      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="e">
         <f t="shared" si="0"/>
-        <v>9.0760000000000023</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A10" s="16"/>
-      <c r="B10" s="15">
+      <c r="A10" s="22"/>
+      <c r="B10" s="21">
         <v>1.5689999999999999E-2</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="1">
-        <v>20</v>
-      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="1">
         <f>$N$10-D10-F10</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
-        <v>20</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
       <c r="H10" s="1">
         <f>$N$10-G10-I10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I10" s="1"/>
       <c r="J10" s="7">
         <f>(D10+G10)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="2">
-        <v>8.57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="M10" t="s">
         <v>9</v>
       </c>
@@ -1282,507 +1248,385 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="4">
         <v>2</v>
       </c>
-      <c r="D11">
-        <v>20</v>
-      </c>
       <c r="E11">
         <f t="shared" ref="E11:E14" si="1">$N$10-D11-F11</f>
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
         <v>20</v>
       </c>
       <c r="H11">
         <f t="shared" ref="H11:H14" si="2">$N$10-G11-I11</f>
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J11" s="3">
         <f>(D11+G11)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K11" s="4">
-        <v>9.1199999999999992</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="4">
         <v>3</v>
       </c>
-      <c r="D12">
-        <v>20</v>
-      </c>
       <c r="E12">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
         <v>20</v>
       </c>
       <c r="H12">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" ref="J12:J14" si="3">(D12+G12)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K12" s="4">
-        <v>8.48</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="4"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="4">
         <v>4</v>
       </c>
-      <c r="D13">
-        <v>20</v>
-      </c>
       <c r="E13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
         <v>20</v>
       </c>
       <c r="H13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K13" s="4">
-        <v>9.0399999999999991</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K13" s="4"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="4">
         <v>5</v>
       </c>
-      <c r="D14">
-        <v>19</v>
-      </c>
       <c r="E14">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
         <v>20</v>
       </c>
       <c r="H14">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="3"/>
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="K14" s="4">
-        <v>8.57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="9" t="e">
         <f>AVERAGE(D10:D14)</f>
-        <v>19.8</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" ref="E15" si="4">AVERAGE(E10:E14)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="9">
+        <v>20</v>
+      </c>
+      <c r="F15" s="9" t="e">
         <f t="shared" ref="F15" si="5">AVERAGE(F10:F14)</f>
-        <v>0.2</v>
-      </c>
-      <c r="G15" s="9">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="9" t="e">
         <f t="shared" ref="G15" si="6">AVERAGE(G10:G14)</f>
-        <v>20</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H15" s="9">
         <f t="shared" ref="H15" si="7">AVERAGE(H10:H14)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="9">
+        <v>20</v>
+      </c>
+      <c r="I15" s="9" t="e">
         <f t="shared" ref="I15" si="8">AVERAGE(I10:I14)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J15" s="11">
         <f t="shared" ref="J15" si="9">AVERAGE(J10:J14)</f>
-        <v>0.99499999999999988</v>
-      </c>
-      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="e">
         <f t="shared" ref="K15" si="10">AVERAGE(K10:K14)</f>
-        <v>8.7559999999999985</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A16" s="16"/>
-      <c r="B16" s="15">
+      <c r="A16" s="22"/>
+      <c r="B16" s="21">
         <v>3.1370000000000002E-2</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
       </c>
-      <c r="D16" s="1">
-        <v>20</v>
-      </c>
+      <c r="D16" s="1"/>
       <c r="E16" s="1">
         <f>$N$10-D16-F16</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>20</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
       <c r="H16" s="1">
         <f>$N$10-G16-I16</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I16" s="1"/>
       <c r="J16" s="7">
         <f>(D16+G16)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K16" s="2">
-        <v>8.4700000000000006</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="4">
         <v>2</v>
       </c>
-      <c r="D17">
-        <v>20</v>
-      </c>
       <c r="E17">
         <f t="shared" ref="E17:E20" si="11">$N$10-D17-F17</f>
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
         <v>20</v>
       </c>
       <c r="H17">
         <f t="shared" ref="H17:H20" si="12">$N$10-G17-I17</f>
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J17" s="3">
         <f>(D17+G17)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K17" s="4">
-        <v>10.119999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K17" s="4"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="4">
         <v>3</v>
       </c>
-      <c r="D18">
-        <v>20</v>
-      </c>
       <c r="E18">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
         <v>20</v>
       </c>
       <c r="H18">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" ref="J18:J20" si="13">(D18+G18)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K18" s="4">
-        <v>8.4600000000000009</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="4">
         <v>4</v>
       </c>
-      <c r="D19">
-        <v>20</v>
-      </c>
       <c r="E19">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
         <v>20</v>
       </c>
       <c r="H19">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="K19" s="4">
-        <v>11.54</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K19" s="4"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="4">
         <v>5</v>
       </c>
-      <c r="D20">
-        <v>20</v>
-      </c>
       <c r="E20">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
         <v>20</v>
       </c>
       <c r="H20">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J20" s="3">
         <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="K20" s="4">
-        <v>8.57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K20" s="4"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="9" t="e">
         <f>AVERAGE(D16:D20)</f>
-        <v>20</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E21" s="9">
         <f t="shared" ref="E21" si="14">AVERAGE(E16:E20)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="9">
+        <v>20</v>
+      </c>
+      <c r="F21" s="9" t="e">
         <f t="shared" ref="F21" si="15">AVERAGE(F16:F20)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="9">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G21" s="9" t="e">
         <f t="shared" ref="G21" si="16">AVERAGE(G16:G20)</f>
-        <v>20</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H21" s="9">
         <f t="shared" ref="H21" si="17">AVERAGE(H16:H20)</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="9">
+        <v>20</v>
+      </c>
+      <c r="I21" s="9" t="e">
         <f t="shared" ref="I21" si="18">AVERAGE(I16:I20)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J21" s="5">
         <f t="shared" ref="J21" si="19">AVERAGE(J16:J20)</f>
-        <v>1</v>
-      </c>
-      <c r="K21" s="10">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="e">
         <f t="shared" ref="K21" si="20">AVERAGE(K16:K20)</f>
-        <v>9.4320000000000004</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="12" t="e">
         <f>_xlfn.STDEV.S(D4:D8)</f>
-        <v>0.89442719099991586</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E22" s="12">
         <f>_xlfn.STDEV.S(E4:E8)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="12" t="e">
         <f>_xlfn.STDEV.S(F4:F8)</f>
-        <v>0.89442719099991586</v>
-      </c>
-      <c r="G22" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G22" s="12" t="e">
         <f t="shared" ref="G22:K22" si="21">_xlfn.STDEV.S(G4:G8)</f>
-        <v>0.44721359549995793</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="12" t="e">
         <f t="shared" si="21"/>
-        <v>0.44721359549995793</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J22" s="12">
         <f>_xlfn.STDEV.S(J4:J8)</f>
-        <v>2.0916500663351906E-2</v>
-      </c>
-      <c r="K22" s="12">
+        <v>0</v>
+      </c>
+      <c r="K22" s="12" t="e">
         <f t="shared" si="21"/>
-        <v>0.52338322479804367</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="12" t="e">
         <f>_xlfn.STDEV.S(D10:D14)</f>
-        <v>0.44721359549995793</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E23" s="12">
         <f t="shared" ref="E23:K23" si="22">_xlfn.STDEV.S(E10:E14)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="12" t="e">
         <f t="shared" si="22"/>
-        <v>0.44721359549995793</v>
-      </c>
-      <c r="G23" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G23" s="12" t="e">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="12" t="e">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J23" s="12">
         <f t="shared" si="22"/>
-        <v>1.1180339887498959E-2</v>
-      </c>
-      <c r="K23" s="12">
+        <v>0</v>
+      </c>
+      <c r="K23" s="12" t="e">
         <f t="shared" si="22"/>
-        <v>0.29938269823087577</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="12" t="e">
         <f>_xlfn.STDEV.S(D16:D20)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E24" s="12">
         <f t="shared" ref="E24:K24" si="23">_xlfn.STDEV.S(E16:E20)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="12" t="e">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G24" s="12" t="e">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="12" t="e">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J24" s="12">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="12" t="e">
         <f t="shared" si="23"/>
-        <v>1.3720677825821823</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="21">
         <v>7.8399999999999997E-3</v>
       </c>
       <c r="C27" s="2">
@@ -1813,148 +1657,92 @@
         <v>1</v>
       </c>
       <c r="K27" s="2">
-        <v>8.49</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
       <c r="C28" s="4">
         <v>2</v>
       </c>
-      <c r="D28">
-        <v>20</v>
-      </c>
       <c r="E28">
         <f>$N$10-D28-F28</f>
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
         <v>20</v>
       </c>
       <c r="H28">
         <f>$N$10-G28-I28</f>
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J28" s="3">
         <f>(D28+G28)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K28" s="4">
-        <v>10.29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K28" s="4"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
       <c r="C29" s="4">
         <v>3</v>
       </c>
-      <c r="D29">
-        <v>20</v>
-      </c>
       <c r="E29">
         <f t="shared" ref="E29:E31" si="24">$N$10-D29-F29</f>
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H29">
         <f>$N$10-G29-I29</f>
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J29" s="3">
         <f>(D29+G29)/($N$10*2)</f>
-        <v>0.95</v>
-      </c>
-      <c r="K29" s="4">
-        <v>8.58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K29" s="4"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
       <c r="C30" s="4">
         <v>4</v>
       </c>
-      <c r="D30">
-        <v>20</v>
-      </c>
       <c r="E30">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
         <v>20</v>
       </c>
       <c r="H30">
         <f t="shared" ref="H30:H31" si="25">$N$10-G30-I30</f>
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J30" s="3">
         <f>(D30+G30)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K30" s="4">
-        <v>8.43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K30" s="4"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="4">
         <v>5</v>
       </c>
-      <c r="D31">
-        <v>20</v>
-      </c>
       <c r="E31">
         <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
         <v>20</v>
       </c>
       <c r="H31">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J31" s="3">
         <f>(D31+G31)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K31" s="4">
-        <v>10.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K31" s="4"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A32" s="16"/>
-      <c r="B32" s="17"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="23"/>
       <c r="C32" s="8" t="s">
         <v>8</v>
       </c>
@@ -1964,7 +1752,7 @@
       </c>
       <c r="E32" s="9">
         <f t="shared" ref="E32" si="26">AVERAGE(E27:E31)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F32" s="9">
         <f t="shared" ref="F32" si="27">AVERAGE(F27:F31)</f>
@@ -1972,573 +1760,3581 @@
       </c>
       <c r="G32" s="9">
         <f t="shared" ref="G32" si="28">AVERAGE(G27:G31)</f>
-        <v>19.600000000000001</v>
+        <v>20</v>
       </c>
       <c r="H32" s="9">
         <f t="shared" ref="H32" si="29">AVERAGE(H27:H31)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I32" s="9">
         <f t="shared" ref="I32" si="30">AVERAGE(I27:I31)</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J32" s="5">
         <f t="shared" ref="J32" si="31">AVERAGE(J27:J31)</f>
-        <v>0.99</v>
+        <v>0.2</v>
       </c>
       <c r="K32" s="10">
         <f t="shared" ref="K32" si="32">AVERAGE(K27:K31)</f>
-        <v>9.16</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A33" s="16"/>
-      <c r="B33" s="15">
+      <c r="A33" s="22"/>
+      <c r="B33" s="21">
         <v>1.5689999999999999E-2</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
       </c>
-      <c r="D33" s="1">
-        <v>20</v>
-      </c>
+      <c r="D33" s="1"/>
       <c r="E33">
         <f t="shared" ref="E33:E37" si="33">$N$10-D33-F33</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="1">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1">
-        <v>19</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
       <c r="H33">
         <f t="shared" ref="H33:H37" si="34">$N$10-G33-I33</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
-        <v>1</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I33" s="1"/>
       <c r="J33" s="7">
         <f>(D33+G33)/($N$10*2)</f>
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="K33" s="2">
-        <v>8.58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K33" s="2"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
       <c r="C34" s="4">
         <v>2</v>
       </c>
-      <c r="D34">
-        <v>20</v>
-      </c>
       <c r="E34">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
         <v>20</v>
       </c>
       <c r="H34">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J34" s="3">
         <f t="shared" ref="J34:J37" si="35">(D34+G34)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K34" s="4">
-        <v>9.93</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K34" s="4"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A35" s="16"/>
-      <c r="B35" s="16"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
       <c r="C35" s="4">
         <v>3</v>
       </c>
-      <c r="D35">
-        <v>20</v>
-      </c>
       <c r="E35">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
         <v>20</v>
       </c>
       <c r="H35">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J35" s="3">
         <f t="shared" si="35"/>
-        <v>1</v>
-      </c>
-      <c r="K35" s="4">
-        <v>8.4700000000000006</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K35" s="4"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
       <c r="C36" s="4">
         <v>4</v>
       </c>
-      <c r="D36">
-        <v>19</v>
-      </c>
       <c r="E36">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J36" s="3">
         <f t="shared" si="35"/>
-        <v>0.95</v>
-      </c>
-      <c r="K36" s="4">
-        <v>8.6300000000000008</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K36" s="4"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
       <c r="C37" s="4">
         <v>5</v>
       </c>
-      <c r="D37">
-        <v>20</v>
-      </c>
       <c r="E37">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
         <v>20</v>
       </c>
       <c r="H37">
         <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J37" s="3">
         <f t="shared" si="35"/>
-        <v>1</v>
-      </c>
-      <c r="K37" s="4">
-        <v>9.76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="23"/>
       <c r="C38" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="9" t="e">
         <f>AVERAGE(D33:D37)</f>
-        <v>19.8</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E38" s="9">
         <f t="shared" ref="E38" si="36">AVERAGE(E33:E37)</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="9">
+        <v>20</v>
+      </c>
+      <c r="F38" s="9" t="e">
         <f t="shared" ref="F38" si="37">AVERAGE(F33:F37)</f>
-        <v>0.2</v>
-      </c>
-      <c r="G38" s="9">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G38" s="9" t="e">
         <f t="shared" ref="G38" si="38">AVERAGE(G33:G37)</f>
-        <v>19.600000000000001</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H38" s="9">
         <f t="shared" ref="H38" si="39">AVERAGE(H33:H37)</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="9">
+        <v>20</v>
+      </c>
+      <c r="I38" s="9" t="e">
         <f t="shared" ref="I38" si="40">AVERAGE(I33:I37)</f>
-        <v>0.4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J38" s="5">
         <f t="shared" ref="J38" si="41">AVERAGE(J33:J37)</f>
-        <v>0.98499999999999999</v>
-      </c>
-      <c r="K38" s="10">
+        <v>0</v>
+      </c>
+      <c r="K38" s="10" t="e">
         <f t="shared" ref="K38" si="42">AVERAGE(K33:K37)</f>
-        <v>9.0739999999999998</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A39" s="16"/>
-      <c r="B39" s="15">
+      <c r="A39" s="22"/>
+      <c r="B39" s="21">
         <v>3.1370000000000002E-2</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
       </c>
-      <c r="D39" s="1">
-        <v>20</v>
-      </c>
+      <c r="D39" s="1"/>
       <c r="E39" s="1">
         <f>$N$10-D39-F39</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>20</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
       <c r="H39" s="1">
         <f>$N$10-G39-I39</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I39" s="1"/>
       <c r="J39" s="7">
         <f>(D39+G39)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K39" s="2">
-        <v>8.57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K39" s="2"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A40" s="16"/>
-      <c r="B40" s="16"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
       <c r="C40" s="4">
         <v>2</v>
       </c>
-      <c r="D40">
-        <v>20</v>
-      </c>
       <c r="E40">
         <f t="shared" ref="E40:E43" si="43">$N$10-D40-F40</f>
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
         <v>20</v>
       </c>
       <c r="H40">
         <f t="shared" ref="H40:H43" si="44">$N$10-G40-I40</f>
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J40" s="3">
         <f t="shared" ref="J40:J43" si="45">(D40+G40)/($N$10*2)</f>
-        <v>1</v>
-      </c>
-      <c r="K40" s="4">
-        <v>10.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A41" s="16"/>
-      <c r="B41" s="16"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
       <c r="C41" s="4">
         <v>3</v>
       </c>
-      <c r="D41">
-        <v>20</v>
-      </c>
       <c r="E41">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
         <v>20</v>
       </c>
       <c r="H41">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J41" s="3">
         <f t="shared" si="45"/>
-        <v>1</v>
-      </c>
-      <c r="K41" s="4">
-        <v>8.66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K41" s="4"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A42" s="16"/>
-      <c r="B42" s="16"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
       <c r="C42" s="4">
         <v>4</v>
       </c>
-      <c r="D42">
-        <v>20</v>
-      </c>
       <c r="E42">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
         <v>20</v>
       </c>
       <c r="H42">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42" s="3">
         <f t="shared" si="45"/>
-        <v>1</v>
-      </c>
-      <c r="K42" s="4">
-        <v>8.58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K42" s="4"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="16"/>
-      <c r="B43" s="16"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
       <c r="C43" s="4">
         <v>5</v>
       </c>
-      <c r="D43">
-        <v>20</v>
-      </c>
       <c r="E43">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
         <v>20</v>
       </c>
       <c r="H43">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J43" s="3">
         <f t="shared" si="45"/>
-        <v>1</v>
-      </c>
-      <c r="K43" s="4">
-        <v>9.94</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K43" s="4"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
       <c r="C44" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="9" t="e">
         <f>AVERAGE(D39:D43)</f>
-        <v>20</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E44" s="9">
         <f t="shared" ref="E44" si="46">AVERAGE(E39:E43)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="9">
+        <v>20</v>
+      </c>
+      <c r="F44" s="9" t="e">
         <f t="shared" ref="F44" si="47">AVERAGE(F39:F43)</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="9">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G44" s="9" t="e">
         <f t="shared" ref="G44" si="48">AVERAGE(G39:G43)</f>
-        <v>20</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H44" s="9">
         <f t="shared" ref="H44" si="49">AVERAGE(H39:H43)</f>
-        <v>0</v>
-      </c>
-      <c r="I44" s="9">
+        <v>20</v>
+      </c>
+      <c r="I44" s="9" t="e">
         <f t="shared" ref="I44" si="50">AVERAGE(I39:I43)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J44" s="5">
         <f t="shared" ref="J44" si="51">AVERAGE(J39:J43)</f>
-        <v>1</v>
-      </c>
-      <c r="K44" s="10">
+        <v>0</v>
+      </c>
+      <c r="K44" s="10" t="e">
         <f t="shared" ref="K44" si="52">AVERAGE(K39:K43)</f>
-        <v>9.2480000000000011</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
         <v>12</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="12" t="e">
         <f>_xlfn.STDEV.S(D27:D31)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E45" s="12">
         <f>_xlfn.STDEV.S(E27:E31)</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="12">
+        <v>8.9442719099991592</v>
+      </c>
+      <c r="F45" s="12" t="e">
         <f>_xlfn.STDEV.S(F27:F31)</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G45" s="12" t="e">
         <f t="shared" ref="G45:I45" si="53">_xlfn.STDEV.S(G27:G31)</f>
-        <v>0.89442719099991586</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="12">
+        <v>8.9442719099991592</v>
+      </c>
+      <c r="I45" s="12" t="e">
         <f t="shared" si="53"/>
-        <v>0.89442719099991586</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J45" s="12">
         <f>_xlfn.STDEV.S(J27:J31)</f>
-        <v>2.2360679774997918E-2</v>
-      </c>
-      <c r="K45" s="12">
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="K45" s="12" t="e">
         <f t="shared" ref="K45" si="54">_xlfn.STDEV.S(K27:K31)</f>
-        <v>0.91071400560219751</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
         <v>12</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="12" t="e">
         <f>_xlfn.STDEV.S(D33:D37)</f>
-        <v>0.44721359549995793</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E46" s="12">
         <f t="shared" ref="E46:K46" si="55">_xlfn.STDEV.S(E33:E37)</f>
         <v>0</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="12" t="e">
         <f t="shared" si="55"/>
-        <v>0.44721359549995793</v>
-      </c>
-      <c r="G46" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G46" s="12" t="e">
         <f t="shared" si="55"/>
-        <v>0.54772255750516607</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="12" t="e">
         <f t="shared" si="55"/>
-        <v>0.54772255750516607</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J46" s="12">
         <f t="shared" si="55"/>
-        <v>2.2360679774997918E-2</v>
-      </c>
-      <c r="K46" s="12">
+        <v>0</v>
+      </c>
+      <c r="K46" s="12" t="e">
         <f t="shared" si="55"/>
-        <v>0.70875242503994251</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="C47" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="12" t="e">
         <f>_xlfn.STDEV.S(D39:D43)</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="E47" s="12">
         <f t="shared" ref="E47:K47" si="56">_xlfn.STDEV.S(E39:E43)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="12" t="e">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G47" s="12" t="e">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="12" t="e">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="J47" s="12">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="K47" s="12">
+      <c r="K47" s="12" t="e">
         <f t="shared" si="56"/>
-        <v>0.90458277675401266</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A4:A21"/>
-    <mergeCell ref="A27:A44"/>
-    <mergeCell ref="B27:B32"/>
-    <mergeCell ref="B33:B38"/>
-    <mergeCell ref="B39:B44"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="B16:B21"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A21"/>
+    <mergeCell ref="A27:A44"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B33:B38"/>
+    <mergeCell ref="B39:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1240C18-AF1B-4B57-8B4D-525F73D60CBA}">
+  <dimension ref="A2:Q47"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="12.4609375" customWidth="1"/>
+    <col min="10" max="10" width="12.61328125" customWidth="1"/>
+    <col min="13" max="13" width="10.84375" customWidth="1"/>
+    <col min="14" max="14" width="7.07421875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="B3" s="24"/>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="21">
+        <v>7.8399999999999997E-3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1">
+        <f>$N$10-D4-F4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1">
+        <f>$N$10-G4-I4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
+        <f>(D4+G4)/($N$10*2)</f>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="K4" s="2">
+        <v>8.64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <f>$N$10-D5-F5</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>19</v>
+      </c>
+      <c r="H5">
+        <f>$N$10-G5-I5</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <f>(D5+G5)/($N$10*2)</f>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="K5" s="4">
+        <v>8.74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <f>$N$10-D6-F6</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <f>$N$10-G6-I6</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <f>(D6+G6)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K6" s="4">
+        <v>9.7899999999999991</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="4">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <f>$N$10-D7-F7</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <f>$N$10-G7-I7</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <f>(D7+G7)/($N$10*2)</f>
+        <v>0.95</v>
+      </c>
+      <c r="K7" s="4">
+        <v>8.73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <f>$N$10-D8-F8</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <f>$N$10-G8-I8</f>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <f>(D8+G8)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K8" s="4">
+        <v>9.48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="9">
+        <f>AVERAGE(D4:D8)</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" ref="E9:K9" si="0">AVERAGE(E4:E8)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="G9" s="9">
+        <f t="shared" si="0"/>
+        <v>19.8</v>
+      </c>
+      <c r="H9" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J9" s="11">
+        <f t="shared" si="0"/>
+        <v>0.98000000000000009</v>
+      </c>
+      <c r="K9" s="6">
+        <f t="shared" si="0"/>
+        <v>9.0760000000000023</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A10" s="22"/>
+      <c r="B10" s="21">
+        <v>1.5689999999999999E-2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1">
+        <f>$N$10-D10-F10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1">
+        <f>$N$10-G10-I10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <f>(D10+G10)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>8.57</v>
+      </c>
+      <c r="M10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="4">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ref="E11:E14" si="1">$N$10-D11-F11</f>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <f t="shared" ref="H11:H14" si="2">$N$10-G11-I11</f>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <f>(D11+G11)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K11" s="4">
+        <v>9.1199999999999992</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="4">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" ref="J12:J14" si="3">(D12+G12)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K12" s="4">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="4">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <v>9.0399999999999991</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="4">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>19</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>20</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <f t="shared" si="3"/>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="K14" s="4">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="9">
+        <f>AVERAGE(D10:D14)</f>
+        <v>19.8</v>
+      </c>
+      <c r="E15" s="9">
+        <f t="shared" ref="E15:K15" si="4">AVERAGE(E10:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="9">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="H15" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="11">
+        <f t="shared" si="4"/>
+        <v>0.99499999999999988</v>
+      </c>
+      <c r="K15" s="6">
+        <f t="shared" si="4"/>
+        <v>8.7559999999999985</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A16" s="22"/>
+      <c r="B16" s="21">
+        <v>3.1370000000000002E-2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1">
+        <f>$N$10-D16-F16</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>20</v>
+      </c>
+      <c r="H16" s="1">
+        <f>$N$10-G16-I16</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7">
+        <f>(D16+G16)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K16" s="2">
+        <v>8.4700000000000006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ref="E17:E20" si="5">$N$10-D17-F17</f>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17">
+        <f t="shared" ref="H17:H20" si="6">$N$10-G17-I17</f>
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <f>(D17+G17)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K17" s="4">
+        <v>10.119999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="4">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>20</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <f t="shared" ref="J18:J20" si="7">(D18+G18)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K18" s="4">
+        <v>8.4600000000000009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>20</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K19" s="4">
+        <v>11.54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="4">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>20</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>20</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="K20" s="4">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="9">
+        <f>AVERAGE(D16:D20)</f>
+        <v>20</v>
+      </c>
+      <c r="E21" s="9">
+        <f t="shared" ref="E21:K21" si="8">AVERAGE(E16:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="8"/>
+        <v>9.4320000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="12">
+        <f>_xlfn.STDEV.S(D4:D8)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="E22" s="12">
+        <f>_xlfn.STDEV.S(E4:E8)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="12">
+        <f>_xlfn.STDEV.S(F4:F8)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="G22" s="12">
+        <f t="shared" ref="G22:K22" si="9">_xlfn.STDEV.S(G4:G8)</f>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="H22" s="12">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="12">
+        <f t="shared" si="9"/>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="J22" s="12">
+        <f>_xlfn.STDEV.S(J4:J8)</f>
+        <v>2.0916500663351906E-2</v>
+      </c>
+      <c r="K22" s="12">
+        <f t="shared" si="9"/>
+        <v>0.52338322479804367</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="12">
+        <f>_xlfn.STDEV.S(D10:D14)</f>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="E23" s="12">
+        <f t="shared" ref="E23:K23" si="10">_xlfn.STDEV.S(E10:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="12">
+        <f t="shared" si="10"/>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="G23" s="12">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="12">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="12">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="12">
+        <f t="shared" si="10"/>
+        <v>1.1180339887498959E-2</v>
+      </c>
+      <c r="K23" s="12">
+        <f t="shared" si="10"/>
+        <v>0.29938269823087577</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="12">
+        <f>_xlfn.STDEV.S(D16:D20)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="12">
+        <f t="shared" ref="E24:K24" si="11">_xlfn.STDEV.S(E16:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="12">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="12">
+        <f t="shared" si="11"/>
+        <v>1.3720677825821823</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="Q26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A27" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="21">
+        <v>7.8399999999999997E-3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="1">
+        <v>20</v>
+      </c>
+      <c r="E27" s="1">
+        <f>$N$10-D27-F27</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>20</v>
+      </c>
+      <c r="H27" s="1">
+        <f>$N$10-G27-I27</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7">
+        <f>(D27+G27)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K27" s="2">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="4">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>20</v>
+      </c>
+      <c r="E28">
+        <f>$N$10-D28-F28</f>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>20</v>
+      </c>
+      <c r="H28">
+        <f>$N$10-G28-I28</f>
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <f>(D28+G28)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K28" s="4">
+        <v>10.29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="4">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>20</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ref="E29:E31" si="12">$N$10-D29-F29</f>
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>18</v>
+      </c>
+      <c r="H29">
+        <f>$N$10-G29-I29</f>
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" s="3">
+        <f>(D29+G29)/($N$10*2)</f>
+        <v>0.95</v>
+      </c>
+      <c r="K29" s="4">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="4">
+        <v>4</v>
+      </c>
+      <c r="D30">
+        <v>20</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>20</v>
+      </c>
+      <c r="H30">
+        <f t="shared" ref="H30:H31" si="13">$N$10-G30-I30</f>
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <f>(D30+G30)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K30" s="4">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="4">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>20</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>20</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <f>(D31+G31)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K31" s="4">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A32" s="22"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="9">
+        <f>AVERAGE(D27:D31)</f>
+        <v>20</v>
+      </c>
+      <c r="E32" s="9">
+        <f t="shared" ref="E32:K32" si="14">AVERAGE(E27:E31)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <f t="shared" si="14"/>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="H32" s="9">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <f t="shared" si="14"/>
+        <v>0.4</v>
+      </c>
+      <c r="J32" s="5">
+        <f t="shared" si="14"/>
+        <v>0.99</v>
+      </c>
+      <c r="K32" s="10">
+        <f t="shared" si="14"/>
+        <v>9.16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A33" s="22"/>
+      <c r="B33" s="21">
+        <v>1.5689999999999999E-2</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>20</v>
+      </c>
+      <c r="E33">
+        <f t="shared" ref="E33:E37" si="15">$N$10-D33-F33</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>19</v>
+      </c>
+      <c r="H33">
+        <f t="shared" ref="H33:H37" si="16">$N$10-G33-I33</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="7">
+        <f>(D33+G33)/($N$10*2)</f>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="K33" s="2">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="4">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>20</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>20</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <f t="shared" ref="J34:J37" si="17">(D34+G34)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K34" s="4">
+        <v>9.93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="4">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>20</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>20</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="K35" s="4">
+        <v>8.4700000000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="4">
+        <v>4</v>
+      </c>
+      <c r="D36">
+        <v>19</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>19</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
+        <f t="shared" si="17"/>
+        <v>0.95</v>
+      </c>
+      <c r="K36" s="4">
+        <v>8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="4">
+        <v>5</v>
+      </c>
+      <c r="D37">
+        <v>20</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>20</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="K37" s="4">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A38" s="22"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="9">
+        <f>AVERAGE(D33:D37)</f>
+        <v>19.8</v>
+      </c>
+      <c r="E38" s="9">
+        <f t="shared" ref="E38:K38" si="18">AVERAGE(E33:E37)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="9">
+        <f t="shared" si="18"/>
+        <v>0.2</v>
+      </c>
+      <c r="G38" s="9">
+        <f t="shared" si="18"/>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="H38" s="9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="9">
+        <f t="shared" si="18"/>
+        <v>0.4</v>
+      </c>
+      <c r="J38" s="5">
+        <f t="shared" si="18"/>
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="K38" s="10">
+        <f t="shared" si="18"/>
+        <v>9.0739999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A39" s="22"/>
+      <c r="B39" s="21">
+        <v>3.1370000000000002E-2</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1">
+        <v>20</v>
+      </c>
+      <c r="E39" s="1">
+        <f>$N$10-D39-F39</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>20</v>
+      </c>
+      <c r="H39" s="1">
+        <f>$N$10-G39-I39</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="7">
+        <f>(D39+G39)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K39" s="2">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="4">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>20</v>
+      </c>
+      <c r="E40">
+        <f t="shared" ref="E40:E43" si="19">$N$10-D40-F40</f>
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>20</v>
+      </c>
+      <c r="H40">
+        <f t="shared" ref="H40:H43" si="20">$N$10-G40-I40</f>
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <f t="shared" ref="J40:J43" si="21">(D40+G40)/($N$10*2)</f>
+        <v>1</v>
+      </c>
+      <c r="K40" s="4">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="4">
+        <v>3</v>
+      </c>
+      <c r="D41">
+        <v>20</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>20</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="K41" s="4">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="4">
+        <v>4</v>
+      </c>
+      <c r="D42">
+        <v>20</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>20</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="K42" s="4">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="4">
+        <v>5</v>
+      </c>
+      <c r="D43">
+        <v>20</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>20</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="K43" s="4">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="9">
+        <f>AVERAGE(D39:D43)</f>
+        <v>20</v>
+      </c>
+      <c r="E44" s="9">
+        <f t="shared" ref="E44:K44" si="22">AVERAGE(E39:E43)</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="9">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="9">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="H44" s="9">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="9">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="5">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="K44" s="10">
+        <f t="shared" si="22"/>
+        <v>9.2480000000000011</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="12">
+        <f>_xlfn.STDEV.S(D27:D31)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="12">
+        <f>_xlfn.STDEV.S(E27:E31)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="12">
+        <f>_xlfn.STDEV.S(F27:F31)</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="12">
+        <f t="shared" ref="G45:I45" si="23">_xlfn.STDEV.S(G27:G31)</f>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="H45" s="12">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="12">
+        <f t="shared" si="23"/>
+        <v>0.89442719099991586</v>
+      </c>
+      <c r="J45" s="12">
+        <f>_xlfn.STDEV.S(J27:J31)</f>
+        <v>2.2360679774997918E-2</v>
+      </c>
+      <c r="K45" s="12">
+        <f t="shared" ref="K45" si="24">_xlfn.STDEV.S(K27:K31)</f>
+        <v>0.91071400560219751</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="12">
+        <f>_xlfn.STDEV.S(D33:D37)</f>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="E46" s="12">
+        <f t="shared" ref="E46:K46" si="25">_xlfn.STDEV.S(E33:E37)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="12">
+        <f t="shared" si="25"/>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="G46" s="12">
+        <f t="shared" si="25"/>
+        <v>0.54772255750516607</v>
+      </c>
+      <c r="H46" s="12">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="12">
+        <f t="shared" si="25"/>
+        <v>0.54772255750516607</v>
+      </c>
+      <c r="J46" s="12">
+        <f t="shared" si="25"/>
+        <v>2.2360679774997918E-2</v>
+      </c>
+      <c r="K46" s="12">
+        <f t="shared" si="25"/>
+        <v>0.70875242503994251</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="12">
+        <f>_xlfn.STDEV.S(D39:D43)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="12">
+        <f t="shared" ref="E47:K47" si="26">_xlfn.STDEV.S(E39:E43)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="12">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="12">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="12">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="12">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="12">
+        <f t="shared" si="26"/>
+        <v>0.90458277675401266</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A27:A44"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B33:B38"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A4:A21"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="B16:B21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1220CD30-59C2-4EC2-80C1-3346DDB8090E}">
+  <dimension ref="A2:M65"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3046875" customWidth="1"/>
+    <col min="7" max="7" width="9.3828125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="C2" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A4" s="20">
+        <v>7.8399999999999997E-3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" s="15">
+        <f>C4/$M$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="17">
+        <f>H4/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A5" s="20"/>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="15">
+        <f>C5/$M$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="17">
+        <f>H5/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A6" s="20"/>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" s="15">
+        <f>C6/$M$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="17">
+        <f>H6/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A7" s="20"/>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" s="15">
+        <f>C7/$M$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="17">
+        <f>H7/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A8" s="20"/>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" s="15">
+        <f>C8/$M$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="17">
+        <f>H8/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="12">
+        <f>AVERAGE(C4:C8)</f>
+        <v>15</v>
+      </c>
+      <c r="D9" s="12">
+        <f t="shared" ref="D9:F9" si="0">AVERAGE(D4:D8)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="12">
+        <f t="shared" si="0"/>
+        <v>4.8</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12" t="e">
+        <f t="shared" ref="H9:K9" si="1">AVERAGE(H4:H8)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I9" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="12" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K9" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="12">
+        <f>_xlfn.STDEV.S(C4:C8)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" ref="D10:F10" si="2">_xlfn.STDEV.S(D4:D8)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="2"/>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="F10" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12" t="e">
+        <f t="shared" ref="H10:K10" si="3">_xlfn.STDEV.S(H4:H8)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I10" s="12" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J10" s="12" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="C13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="C14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A15" s="20">
+        <v>1.5689999999999999E-2</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17">
+        <f>C15/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17">
+        <f>H15/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A16" s="20"/>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17">
+        <f>C16/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="17">
+        <f>H16/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A17" s="20"/>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17">
+        <f>C17/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="17">
+        <f>H17/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A18" s="20"/>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="17">
+        <f>C18/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="17">
+        <f>H18/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A19" s="20"/>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="17">
+        <f>C19/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="17">
+        <f>H19/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="12" t="e">
+        <f>AVERAGE(C15:C19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D20" s="12" t="e">
+        <f t="shared" ref="D20" si="4">AVERAGE(D15:D19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E20" s="12" t="e">
+        <f t="shared" ref="E20" si="5">AVERAGE(E15:E19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F20" s="15">
+        <f t="shared" ref="F20" si="6">AVERAGE(F15:F19)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12" t="e">
+        <f t="shared" ref="H20" si="7">AVERAGE(H15:H19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I20" s="12" t="e">
+        <f t="shared" ref="I20" si="8">AVERAGE(I15:I19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J20" s="12" t="e">
+        <f t="shared" ref="J20" si="9">AVERAGE(J15:J19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K20" s="15">
+        <f t="shared" ref="K20" si="10">AVERAGE(K15:K19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="12" t="e">
+        <f>_xlfn.STDEV.S(C15:C19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D21" s="12" t="e">
+        <f t="shared" ref="D21:F21" si="11">_xlfn.STDEV.S(D15:D19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E21" s="12" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F21" s="15">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12" t="e">
+        <f t="shared" ref="H21:K21" si="12">_xlfn.STDEV.S(H15:H19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I21" s="12" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J21" s="12" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K21" s="12">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C24" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A26" s="20">
+        <v>3.1370000000000002E-2</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="17">
+        <f>C26/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="17">
+        <f>H26/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A27" s="20"/>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="17">
+        <f>C27/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="17">
+        <f>H27/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A28" s="20"/>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="17">
+        <f>C28/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="12"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="17">
+        <f>H28/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A29" s="20"/>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="17">
+        <f>C29/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="17">
+        <f>H29/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A30" s="20"/>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="17">
+        <f>C30/$M$7</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="12"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="17">
+        <f>H30/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="12" t="e">
+        <f>AVERAGE(C26:C30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D31" s="12" t="e">
+        <f t="shared" ref="D31" si="13">AVERAGE(D26:D30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E31" s="12" t="e">
+        <f t="shared" ref="E31" si="14">AVERAGE(E26:E30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F31" s="15">
+        <f t="shared" ref="F31" si="15">AVERAGE(F26:F30)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12" t="e">
+        <f t="shared" ref="H31" si="16">AVERAGE(H26:H30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I31" s="12" t="e">
+        <f t="shared" ref="I31" si="17">AVERAGE(I26:I30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J31" s="12" t="e">
+        <f t="shared" ref="J31" si="18">AVERAGE(J26:J30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K31" s="15">
+        <f t="shared" ref="K31" si="19">AVERAGE(K26:K30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="12" t="e">
+        <f>_xlfn.STDEV.S(C26:C30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D32" s="12" t="e">
+        <f t="shared" ref="D32:K32" si="20">_xlfn.STDEV.S(D26:D30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E32" s="12" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F32" s="15">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I32" s="12" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J32" s="12" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K32" s="12">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C35" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" t="s">
+        <v>5</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A37" s="20">
+        <v>7.8399999999999997E-3</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" s="15">
+        <f>C37/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G37" s="12"/>
+      <c r="H37">
+        <v>18</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37" s="15">
+        <f>H37/$M$7</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A38" s="20"/>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38" s="15">
+        <f>C38/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G38" s="12"/>
+      <c r="H38">
+        <v>18</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="K38" s="15">
+        <f>H38/$M$7</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A39" s="20"/>
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39">
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39" s="15">
+        <f>C39/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G39" s="12"/>
+      <c r="H39">
+        <v>18</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39" s="15">
+        <f>H39/$M$7</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A40" s="20"/>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>20</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40" s="15">
+        <f>C40/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G40" s="12"/>
+      <c r="H40">
+        <v>18</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40" s="15">
+        <f>H40/$M$7</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A41" s="20"/>
+      <c r="B41">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <v>20</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41" s="15">
+        <f>C41/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G41" s="12"/>
+      <c r="H41">
+        <v>18</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" s="18">
+        <f>H41/$M$7</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="12">
+        <f>AVERAGE(C37:C41)</f>
+        <v>20</v>
+      </c>
+      <c r="D42" s="12">
+        <f t="shared" ref="D42" si="21">AVERAGE(D37:D41)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="12">
+        <f t="shared" ref="E42" si="22">AVERAGE(E37:E41)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="15">
+        <f t="shared" ref="F42" si="23">AVERAGE(F37:F41)</f>
+        <v>1</v>
+      </c>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12">
+        <f t="shared" ref="H42" si="24">AVERAGE(H37:H41)</f>
+        <v>18</v>
+      </c>
+      <c r="I42" s="12">
+        <f t="shared" ref="I42" si="25">AVERAGE(I37:I41)</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="12">
+        <f t="shared" ref="J42" si="26">AVERAGE(J37:J41)</f>
+        <v>2</v>
+      </c>
+      <c r="K42" s="15">
+        <f t="shared" ref="K42" si="27">AVERAGE(K37:K41)</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="12">
+        <f>_xlfn.STDEV.S(C37:C41)</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="12">
+        <f t="shared" ref="D43:F43" si="28">_xlfn.STDEV.S(D37:D41)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="12">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12">
+        <f t="shared" ref="H43:K43" si="29">_xlfn.STDEV.S(H37:H41)</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="12">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="12">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="12">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C46" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C47" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>2</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A48" s="20">
+        <v>1.5689999999999999E-2</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" s="15">
+        <f>C48/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G48" s="12"/>
+      <c r="H48">
+        <v>10</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>10</v>
+      </c>
+      <c r="K48" s="15">
+        <f>H48/$M$7</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A49" s="20"/>
+      <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="C49" s="25">
+        <v>20</v>
+      </c>
+      <c r="D49" s="25">
+        <v>0</v>
+      </c>
+      <c r="E49" s="25">
+        <v>0</v>
+      </c>
+      <c r="F49" s="18">
+        <f>C49/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G49" s="12"/>
+      <c r="H49">
+        <v>11</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9</v>
+      </c>
+      <c r="K49" s="15">
+        <f>H49/$M$7</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A50" s="20"/>
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50" s="25">
+        <v>19</v>
+      </c>
+      <c r="D50" s="25">
+        <v>0</v>
+      </c>
+      <c r="E50" s="25">
+        <v>1</v>
+      </c>
+      <c r="F50" s="18">
+        <f>C50/$M$7</f>
+        <v>0.95</v>
+      </c>
+      <c r="G50" s="12"/>
+      <c r="H50">
+        <v>11</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9</v>
+      </c>
+      <c r="K50" s="15">
+        <f>H50/$M$7</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A51" s="20"/>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51">
+        <v>20</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" s="15">
+        <f>C51/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G51" s="12"/>
+      <c r="H51">
+        <v>11</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9</v>
+      </c>
+      <c r="K51" s="15">
+        <f>H51/$M$7</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A52" s="20"/>
+      <c r="B52">
+        <v>5</v>
+      </c>
+      <c r="C52">
+        <v>20</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52" s="15">
+        <f>C52/$M$7</f>
+        <v>1</v>
+      </c>
+      <c r="G52" s="12"/>
+      <c r="H52">
+        <v>11</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9</v>
+      </c>
+      <c r="K52" s="15">
+        <f>H52/$M$7</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="12">
+        <f>AVERAGE(C48:C52)</f>
+        <v>19.8</v>
+      </c>
+      <c r="D53" s="12">
+        <f t="shared" ref="D53" si="30">AVERAGE(D48:D52)</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="12">
+        <f t="shared" ref="E53" si="31">AVERAGE(E48:E52)</f>
+        <v>0.2</v>
+      </c>
+      <c r="F53" s="15">
+        <f t="shared" ref="F53" si="32">AVERAGE(F48:F52)</f>
+        <v>0.99</v>
+      </c>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12">
+        <f t="shared" ref="H53" si="33">AVERAGE(H48:H52)</f>
+        <v>10.8</v>
+      </c>
+      <c r="I53" s="12">
+        <f t="shared" ref="I53" si="34">AVERAGE(I48:I52)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="12">
+        <f t="shared" ref="J53" si="35">AVERAGE(J48:J52)</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="K53" s="15">
+        <f t="shared" ref="K53" si="36">AVERAGE(K48:K52)</f>
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="12">
+        <f>_xlfn.STDEV.S(C48:C52)</f>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="D54" s="12">
+        <f t="shared" ref="D54:K54" si="37">_xlfn.STDEV.S(D48:D52)</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="12">
+        <f t="shared" si="37"/>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="F54" s="15">
+        <f t="shared" si="37"/>
+        <v>2.2360679774997918E-2</v>
+      </c>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12">
+        <f t="shared" si="37"/>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="I54" s="12">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="12">
+        <f t="shared" si="37"/>
+        <v>0.44721359549995793</v>
+      </c>
+      <c r="K54" s="15">
+        <f t="shared" si="37"/>
+        <v>2.2360679774997918E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C57" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="19"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="C58" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
+        <v>2</v>
+      </c>
+      <c r="J58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A59" s="20">
+        <v>3.1370000000000002E-2</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>19</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" s="15">
+        <f>C59/$M$7</f>
+        <v>0.95</v>
+      </c>
+      <c r="G59" s="12"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="17">
+        <f>H59/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A60" s="20"/>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60">
+        <v>19</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60" s="15">
+        <f>C60/$M$7</f>
+        <v>0.95</v>
+      </c>
+      <c r="G60" s="12"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="17">
+        <f>H60/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A61" s="20"/>
+      <c r="B61">
+        <v>3</v>
+      </c>
+      <c r="C61">
+        <v>19</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61" s="15">
+        <f>C61/$M$7</f>
+        <v>0.95</v>
+      </c>
+      <c r="G61" s="12"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="17">
+        <f>H61/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A62" s="20"/>
+      <c r="B62">
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <v>19</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" s="15">
+        <f>C62/$M$7</f>
+        <v>0.95</v>
+      </c>
+      <c r="G62" s="12"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="17">
+        <f>H62/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A63" s="20"/>
+      <c r="B63">
+        <v>5</v>
+      </c>
+      <c r="C63">
+        <v>19</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63" s="15">
+        <f>C63/$M$7</f>
+        <v>0.95</v>
+      </c>
+      <c r="G63" s="12"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="17">
+        <f>H63/$M$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="12">
+        <f>AVERAGE(C59:C63)</f>
+        <v>19</v>
+      </c>
+      <c r="D64" s="12">
+        <f t="shared" ref="D64" si="38">AVERAGE(D59:D63)</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="12">
+        <f t="shared" ref="E64" si="39">AVERAGE(E59:E63)</f>
+        <v>1</v>
+      </c>
+      <c r="F64" s="15">
+        <f t="shared" ref="F64" si="40">AVERAGE(F59:F63)</f>
+        <v>0.95</v>
+      </c>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12" t="e">
+        <f t="shared" ref="H64" si="41">AVERAGE(H59:H63)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I64" s="12" t="e">
+        <f t="shared" ref="I64" si="42">AVERAGE(I59:I63)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J64" s="12" t="e">
+        <f t="shared" ref="J64" si="43">AVERAGE(J59:J63)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K64" s="15">
+        <f t="shared" ref="K64" si="44">AVERAGE(K59:K63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="12">
+        <f>_xlfn.STDEV.S(C59:C63)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="12">
+        <f t="shared" ref="D65:K65" si="45">_xlfn.STDEV.S(D59:D63)</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="12">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="15">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I65" s="12" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J65" s="12" t="e">
+        <f t="shared" si="45"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K65" s="12">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="A59:A63"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="A48:A52"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="H57:K57"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/paper/test_results.xlsx
+++ b/paper/test_results.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mixture-of-Experts_Research\paper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3161135-5DE9-4A97-905A-AA910B274FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574AF23B-0E19-49D9-9C49-28C081F15084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{7F82E78F-F225-4B75-B204-CA5D83064DD0}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7F82E78F-F225-4B75-B204-CA5D83064DD0}"/>
   </bookViews>
   <sheets>
     <sheet name="Empirical Results Experts" sheetId="2" r:id="rId1"/>
-    <sheet name="Formal Results Router 1" sheetId="5" r:id="rId2"/>
+    <sheet name="Formal Results Router" sheetId="5" r:id="rId2"/>
     <sheet name="Formal Results Expert" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -1146,7 +1146,7 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E5:E8" si="1">$N$10-D6-F6</f>
+        <f t="shared" ref="E6:E8" si="1">$N$10-D6-F6</f>
         <v>0</v>
       </c>
       <c r="F6">
@@ -2408,17 +2408,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A27:A44"/>
+    <mergeCell ref="B27:B32"/>
+    <mergeCell ref="B33:B38"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="A4:A21"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="B16:B21"/>
-    <mergeCell ref="A27:A44"/>
-    <mergeCell ref="B27:B32"/>
-    <mergeCell ref="B33:B38"/>
-    <mergeCell ref="B39:B44"/>
-    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3739,12 +3739,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="H12:K12"/>
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="H22:K22"/>
@@ -3757,6 +3751,12 @@
     <mergeCell ref="A44:A48"/>
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="H52:K52"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="H12:K12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
